--- a/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capabilities" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Inventory" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy Crosswalk" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Method" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Navigation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Method" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Roles &amp; Credentials'!$A$1:$S$27</definedName>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +65,10 @@
       <b val="1"/>
       <color rgb="001B5E20"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
@@ -143,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -214,16 +219,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -13112,7 +13121,2268 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:Y32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="5.5" customWidth="1" min="5" max="5"/>
+    <col width="5.5" customWidth="1" min="6" max="6"/>
+    <col width="5.5" customWidth="1" min="7" max="7"/>
+    <col width="5.5" customWidth="1" min="8" max="8"/>
+    <col width="5.5" customWidth="1" min="9" max="9"/>
+    <col width="5.5" customWidth="1" min="10" max="10"/>
+    <col width="5.5" customWidth="1" min="11" max="11"/>
+    <col width="5.5" customWidth="1" min="12" max="12"/>
+    <col width="5.5" customWidth="1" min="13" max="13"/>
+    <col width="5.5" customWidth="1" min="14" max="14"/>
+    <col width="5.5" customWidth="1" min="15" max="15"/>
+    <col width="5.5" customWidth="1" min="16" max="16"/>
+    <col width="5.5" customWidth="1" min="17" max="17"/>
+    <col width="5.5" customWidth="1" min="18" max="18"/>
+    <col width="5.5" customWidth="1" min="19" max="19"/>
+    <col width="5.5" customWidth="1" min="20" max="20"/>
+    <col width="5.5" customWidth="1" min="21" max="21"/>
+    <col width="5.5" customWidth="1" min="22" max="22"/>
+    <col width="5.5" customWidth="1" min="23" max="23"/>
+    <col width="5.5" customWidth="1" min="24" max="24"/>
+    <col width="5.5" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="150" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Role ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Staff ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Approach</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Fibre &amp; Home</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Customer Search</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>Leads</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>New Connections</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>Existing Service</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>Number Services</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>SIM &amp; Device</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>New Connections</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>Existing Service</t>
+        </is>
+      </c>
+      <c r="W1" s="13" t="inlineStr">
+        <is>
+          <t>Relocation</t>
+        </is>
+      </c>
+      <c r="X1" s="13" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="Y1" s="13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="24" t="n"/>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="25" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="F2" s="25" t="inlineStr">
+        <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="G2" s="25" t="inlineStr">
+        <is>
+          <t>fibre-home</t>
+        </is>
+      </c>
+      <c r="H2" s="25" t="inlineStr">
+        <is>
+          <t>customers</t>
+        </is>
+      </c>
+      <c r="I2" s="25" t="inlineStr">
+        <is>
+          <t>customer-search</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="K2" s="25" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="L2" s="25" t="inlineStr">
+        <is>
+          <t>leads</t>
+        </is>
+      </c>
+      <c r="M2" s="25" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="N2" s="25" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="O2" s="25" t="inlineStr">
+        <is>
+          <t>administration</t>
+        </is>
+      </c>
+      <c r="P2" s="25" t="inlineStr">
+        <is>
+          <t>mobile.new-connections</t>
+        </is>
+      </c>
+      <c r="Q2" s="25" t="inlineStr">
+        <is>
+          <t>mobile.existing-service</t>
+        </is>
+      </c>
+      <c r="R2" s="25" t="inlineStr">
+        <is>
+          <t>mobile.number-services</t>
+        </is>
+      </c>
+      <c r="S2" s="25" t="inlineStr">
+        <is>
+          <t>mobile.sim-device</t>
+        </is>
+      </c>
+      <c r="T2" s="25" t="inlineStr">
+        <is>
+          <t>mobile.support</t>
+        </is>
+      </c>
+      <c r="U2" s="25" t="inlineStr">
+        <is>
+          <t>fibre-home.new-connections</t>
+        </is>
+      </c>
+      <c r="V2" s="25" t="inlineStr">
+        <is>
+          <t>fibre-home.existing-service</t>
+        </is>
+      </c>
+      <c r="W2" s="25" t="inlineStr">
+        <is>
+          <t>fibre-home.relocation</t>
+        </is>
+      </c>
+      <c r="X2" s="25" t="inlineStr">
+        <is>
+          <t>fibre-home.equipment</t>
+        </is>
+      </c>
+      <c r="Y2" s="25" t="inlineStr">
+        <is>
+          <t>fibre-home.support</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-01</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12341</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Retail Sales Agent</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O3" s="21" t="n"/>
+      <c r="P3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y3" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-02</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12342</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Telesales Agent</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="21" t="n"/>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="n"/>
+      <c r="L4" s="21" t="n"/>
+      <c r="M4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="n"/>
+      <c r="P4" s="21" t="n"/>
+      <c r="Q4" s="21" t="n"/>
+      <c r="R4" s="21" t="n"/>
+      <c r="S4" s="21" t="n"/>
+      <c r="T4" s="21" t="n"/>
+      <c r="U4" s="21" t="n"/>
+      <c r="V4" s="21" t="n"/>
+      <c r="W4" s="21" t="n"/>
+      <c r="X4" s="21" t="n"/>
+      <c r="Y4" s="21" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-03</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12343</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Direct Sales Agent</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="n"/>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="n"/>
+      <c r="L5" s="21" t="n"/>
+      <c r="M5" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O5" s="21" t="n"/>
+      <c r="P5" s="21" t="n"/>
+      <c r="Q5" s="21" t="n"/>
+      <c r="R5" s="21" t="n"/>
+      <c r="S5" s="21" t="n"/>
+      <c r="T5" s="21" t="n"/>
+      <c r="U5" s="21" t="n"/>
+      <c r="V5" s="21" t="n"/>
+      <c r="W5" s="21" t="n"/>
+      <c r="X5" s="21" t="n"/>
+      <c r="Y5" s="21" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-04</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12344</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Tablet / Field Sales Agent</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="n"/>
+      <c r="G6" s="21" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="n"/>
+      <c r="L6" s="21" t="n"/>
+      <c r="M6" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O6" s="21" t="n"/>
+      <c r="P6" s="21" t="n"/>
+      <c r="Q6" s="21" t="n"/>
+      <c r="R6" s="21" t="n"/>
+      <c r="S6" s="21" t="n"/>
+      <c r="T6" s="21" t="n"/>
+      <c r="U6" s="21" t="n"/>
+      <c r="V6" s="21" t="n"/>
+      <c r="W6" s="21" t="n"/>
+      <c r="X6" s="21" t="n"/>
+      <c r="Y6" s="21" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-05</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12345</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Mass Market Agent</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="n"/>
+      <c r="L7" s="21" t="n"/>
+      <c r="M7" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O7" s="21" t="n"/>
+      <c r="P7" s="21" t="n"/>
+      <c r="Q7" s="21" t="n"/>
+      <c r="R7" s="21" t="n"/>
+      <c r="S7" s="21" t="n"/>
+      <c r="T7" s="21" t="n"/>
+      <c r="U7" s="21" t="n"/>
+      <c r="V7" s="21" t="n"/>
+      <c r="W7" s="21" t="n"/>
+      <c r="X7" s="21" t="n"/>
+      <c r="Y7" s="21" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-06</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12346</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Account Manager</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="n"/>
+      <c r="L8" s="21" t="n"/>
+      <c r="M8" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O8" s="21" t="n"/>
+      <c r="P8" s="21" t="n"/>
+      <c r="Q8" s="21" t="n"/>
+      <c r="R8" s="21" t="n"/>
+      <c r="S8" s="21" t="n"/>
+      <c r="T8" s="21" t="n"/>
+      <c r="U8" s="21" t="n"/>
+      <c r="V8" s="21" t="n"/>
+      <c r="W8" s="21" t="n"/>
+      <c r="X8" s="21" t="n"/>
+      <c r="Y8" s="21" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-07</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12347</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Key Accounts Manager</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="n"/>
+      <c r="L9" s="21" t="n"/>
+      <c r="M9" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O9" s="21" t="n"/>
+      <c r="P9" s="21" t="n"/>
+      <c r="Q9" s="21" t="n"/>
+      <c r="R9" s="21" t="n"/>
+      <c r="S9" s="21" t="n"/>
+      <c r="T9" s="21" t="n"/>
+      <c r="U9" s="21" t="n"/>
+      <c r="V9" s="21" t="n"/>
+      <c r="W9" s="21" t="n"/>
+      <c r="X9" s="21" t="n"/>
+      <c r="Y9" s="21" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-08</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12348</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Channel Manager</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O10" s="21" t="n"/>
+      <c r="P10" s="21" t="n"/>
+      <c r="Q10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="21" t="n"/>
+      <c r="S10" s="21" t="n"/>
+      <c r="T10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="21" t="n"/>
+      <c r="V10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W10" s="21" t="n"/>
+      <c r="X10" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y10" s="21" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-09</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12349</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Authorized Officer</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="n"/>
+      <c r="L11" s="21" t="n"/>
+      <c r="M11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O11" s="21" t="n"/>
+      <c r="P11" s="21" t="n"/>
+      <c r="Q11" s="21" t="n"/>
+      <c r="R11" s="21" t="n"/>
+      <c r="S11" s="21" t="n"/>
+      <c r="T11" s="21" t="n"/>
+      <c r="U11" s="21" t="n"/>
+      <c r="V11" s="21" t="n"/>
+      <c r="W11" s="21" t="n"/>
+      <c r="X11" s="21" t="n"/>
+      <c r="Y11" s="21" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-10</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12350</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Customer Care Agent</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="n"/>
+      <c r="L12" s="21" t="n"/>
+      <c r="M12" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O12" s="21" t="n"/>
+      <c r="P12" s="21" t="n"/>
+      <c r="Q12" s="21" t="n"/>
+      <c r="R12" s="21" t="n"/>
+      <c r="S12" s="21" t="n"/>
+      <c r="T12" s="21" t="n"/>
+      <c r="U12" s="21" t="n"/>
+      <c r="V12" s="21" t="n"/>
+      <c r="W12" s="21" t="n"/>
+      <c r="X12" s="21" t="n"/>
+      <c r="Y12" s="21" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-11</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12351</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Business Care Agent</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="n"/>
+      <c r="L13" s="21" t="n"/>
+      <c r="M13" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O13" s="21" t="n"/>
+      <c r="P13" s="21" t="n"/>
+      <c r="Q13" s="21" t="n"/>
+      <c r="R13" s="21" t="n"/>
+      <c r="S13" s="21" t="n"/>
+      <c r="T13" s="21" t="n"/>
+      <c r="U13" s="21" t="n"/>
+      <c r="V13" s="21" t="n"/>
+      <c r="W13" s="21" t="n"/>
+      <c r="X13" s="21" t="n"/>
+      <c r="Y13" s="21" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-12</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12352</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Premium Agent</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="n"/>
+      <c r="L14" s="21" t="n"/>
+      <c r="M14" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O14" s="21" t="n"/>
+      <c r="P14" s="21" t="n"/>
+      <c r="Q14" s="21" t="n"/>
+      <c r="R14" s="21" t="n"/>
+      <c r="S14" s="21" t="n"/>
+      <c r="T14" s="21" t="n"/>
+      <c r="U14" s="21" t="n"/>
+      <c r="V14" s="21" t="n"/>
+      <c r="W14" s="21" t="n"/>
+      <c r="X14" s="21" t="n"/>
+      <c r="Y14" s="21" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-13</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12353</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Retention Agent</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="n"/>
+      <c r="L15" s="21" t="n"/>
+      <c r="M15" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N15" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O15" s="21" t="n"/>
+      <c r="P15" s="21" t="n"/>
+      <c r="Q15" s="21" t="n"/>
+      <c r="R15" s="21" t="n"/>
+      <c r="S15" s="21" t="n"/>
+      <c r="T15" s="21" t="n"/>
+      <c r="U15" s="21" t="n"/>
+      <c r="V15" s="21" t="n"/>
+      <c r="W15" s="21" t="n"/>
+      <c r="X15" s="21" t="n"/>
+      <c r="Y15" s="21" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-14</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12354</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Fulfilment Agent</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Product-First</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="n"/>
+      <c r="J16" s="21" t="n"/>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="n"/>
+      <c r="N16" s="21" t="n"/>
+      <c r="O16" s="21" t="n"/>
+      <c r="P16" s="21" t="n"/>
+      <c r="Q16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="21" t="n"/>
+      <c r="S16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="21" t="n"/>
+      <c r="V16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y16" s="21" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-15</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12355</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Back Office Fulfilment Agent</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Product-First</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="n"/>
+      <c r="J17" s="21" t="n"/>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="n"/>
+      <c r="N17" s="21" t="n"/>
+      <c r="O17" s="21" t="n"/>
+      <c r="P17" s="21" t="n"/>
+      <c r="Q17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="21" t="n"/>
+      <c r="S17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="21" t="n"/>
+      <c r="V17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W17" s="21" t="n"/>
+      <c r="X17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y17" s="21" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-16</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12356</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>CDM Agent (Customer Data Management Agent)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="n"/>
+      <c r="G18" s="21" t="n"/>
+      <c r="H18" s="21" t="n"/>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="n"/>
+      <c r="L18" s="21" t="n"/>
+      <c r="M18" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N18" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O18" s="21" t="n"/>
+      <c r="P18" s="21" t="n"/>
+      <c r="Q18" s="21" t="n"/>
+      <c r="R18" s="21" t="n"/>
+      <c r="S18" s="21" t="n"/>
+      <c r="T18" s="21" t="n"/>
+      <c r="U18" s="21" t="n"/>
+      <c r="V18" s="21" t="n"/>
+      <c r="W18" s="21" t="n"/>
+      <c r="X18" s="21" t="n"/>
+      <c r="Y18" s="21" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-17</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12357</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>MNP Agent (Mobile Number Portability Agent)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O19" s="21" t="n"/>
+      <c r="P19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="21" t="n"/>
+      <c r="V19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W19" s="21" t="n"/>
+      <c r="X19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y19" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-18</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12358</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Billing Agent</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="n"/>
+      <c r="L20" s="21" t="n"/>
+      <c r="M20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O20" s="21" t="n"/>
+      <c r="P20" s="21" t="n"/>
+      <c r="Q20" s="21" t="n"/>
+      <c r="R20" s="21" t="n"/>
+      <c r="S20" s="21" t="n"/>
+      <c r="T20" s="21" t="n"/>
+      <c r="U20" s="21" t="n"/>
+      <c r="V20" s="21" t="n"/>
+      <c r="W20" s="21" t="n"/>
+      <c r="X20" s="21" t="n"/>
+      <c r="Y20" s="21" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-19</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12359</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Credit Control Agent</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="21" t="n"/>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="n"/>
+      <c r="L21" s="21" t="n"/>
+      <c r="M21" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N21" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O21" s="21" t="n"/>
+      <c r="P21" s="21" t="n"/>
+      <c r="Q21" s="21" t="n"/>
+      <c r="R21" s="21" t="n"/>
+      <c r="S21" s="21" t="n"/>
+      <c r="T21" s="21" t="n"/>
+      <c r="U21" s="21" t="n"/>
+      <c r="V21" s="21" t="n"/>
+      <c r="W21" s="21" t="n"/>
+      <c r="X21" s="21" t="n"/>
+      <c r="Y21" s="21" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-20</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12360</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Dispatcher</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Product-First</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="n"/>
+      <c r="J22" s="21" t="n"/>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="n"/>
+      <c r="N22" s="21" t="n"/>
+      <c r="O22" s="21" t="n"/>
+      <c r="P22" s="21" t="n"/>
+      <c r="Q22" s="21" t="n"/>
+      <c r="R22" s="21" t="n"/>
+      <c r="S22" s="21" t="n"/>
+      <c r="T22" s="21" t="n"/>
+      <c r="U22" s="21" t="n"/>
+      <c r="V22" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W22" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X22" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y22" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-21</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12361</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Field Engineer</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Product-First</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="n"/>
+      <c r="J23" s="21" t="n"/>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M23" s="21" t="n"/>
+      <c r="N23" s="21" t="n"/>
+      <c r="O23" s="21" t="n"/>
+      <c r="P23" s="21" t="n"/>
+      <c r="Q23" s="21" t="n"/>
+      <c r="R23" s="21" t="n"/>
+      <c r="S23" s="21" t="n"/>
+      <c r="T23" s="21" t="n"/>
+      <c r="U23" s="21" t="n"/>
+      <c r="V23" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W23" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X23" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y23" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-22</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12362</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P24" s="21" t="n"/>
+      <c r="Q24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="21" t="n"/>
+      <c r="S24" s="21" t="n"/>
+      <c r="T24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="21" t="n"/>
+      <c r="V24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-23</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12363</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Manager/Approver</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P25" s="21" t="n"/>
+      <c r="Q25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="21" t="n"/>
+      <c r="S25" s="21" t="n"/>
+      <c r="T25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="21" t="n"/>
+      <c r="V25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W25" s="21" t="n"/>
+      <c r="X25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-24</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12364</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>System Administrator</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Product-First</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="n"/>
+      <c r="J26" s="21" t="n"/>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="n"/>
+      <c r="N26" s="21" t="n"/>
+      <c r="O26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P26" s="21" t="n"/>
+      <c r="Q26" s="21" t="n"/>
+      <c r="R26" s="21" t="n"/>
+      <c r="S26" s="21" t="n"/>
+      <c r="T26" s="21" t="n"/>
+      <c r="U26" s="21" t="n"/>
+      <c r="V26" s="21" t="n"/>
+      <c r="W26" s="21" t="n"/>
+      <c r="X26" s="21" t="n"/>
+      <c r="Y26" s="21" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-25</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12365</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>View Only</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="21" t="n"/>
+      <c r="H27" s="21" t="n"/>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="n"/>
+      <c r="K27" s="21" t="n"/>
+      <c r="L27" s="21" t="n"/>
+      <c r="M27" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N27" s="21" t="n"/>
+      <c r="O27" s="21" t="n"/>
+      <c r="P27" s="21" t="n"/>
+      <c r="Q27" s="21" t="n"/>
+      <c r="R27" s="21" t="n"/>
+      <c r="S27" s="21" t="n"/>
+      <c r="T27" s="21" t="n"/>
+      <c r="U27" s="21" t="n"/>
+      <c r="V27" s="21" t="n"/>
+      <c r="W27" s="21" t="n"/>
+      <c r="X27" s="21" t="n"/>
+      <c r="Y27" s="21" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-26</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12366</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Complaints Agent</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="n"/>
+      <c r="G28" s="21" t="n"/>
+      <c r="H28" s="21" t="n"/>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="n"/>
+      <c r="L28" s="21" t="n"/>
+      <c r="M28" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N28" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O28" s="21" t="n"/>
+      <c r="P28" s="21" t="n"/>
+      <c r="Q28" s="21" t="n"/>
+      <c r="R28" s="21" t="n"/>
+      <c r="S28" s="21" t="n"/>
+      <c r="T28" s="21" t="n"/>
+      <c r="U28" s="21" t="n"/>
+      <c r="V28" s="21" t="n"/>
+      <c r="W28" s="21" t="n"/>
+      <c r="X28" s="21" t="n"/>
+      <c r="Y28" s="21" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Which primary destinations each role sees in the sidebar. Parsed from src/engines/navigationEngine.ts (approach -&gt; ordered subset), src/navigation/navManifest.ts (the closed set of destinations) and src/navigation/journeyCatalogue.ts (which product-line categories a role can reach) — not restated, so it cannot drift from the running app. Indented keys (mobile.*, fibre-home.*) are journey categories inside a product line; both product lines always appear in the rail even where a role reaches none of their categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A30:L32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -13120,346 +15390,358 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>VFQ DXP — Roles, Credentials &amp; Feature Applicability</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>SINGLE SOURCE OF TRUTH for the 26 operational roles. Generated from the app source — do not hand-edit.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Sheets</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Roles &amp; Credentials</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>The role master: all 26 roles with Staff ID, password, group, business unit, approach, channel, context card, the identity each resolves to at login, capability list and legacy crosswalk. Start here.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Applicability Matrix</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Feature x role grid. One column per role (row 1 name, row 2 role id + Staff ID, row 3 approach), one row per catalogued feature.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Capabilities</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Role x action-gate grid. In-surface permissions (resolve a ticket, assign a task, edit customer records) as opposed to "can reach this screen".</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Feature Inventory</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Per feature: key, area, surface, built/planned, screen ids, how many roles hold it, levels granted, and any documented restrictions.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Which sidebar destinations each role sees, including per product-line journey category. Parsed from the navigation source rather than restated, so it cannot drift from the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Legacy Crosswalk</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>The 66-persona -&gt; 26-role mapping, including the 17 legacy personas with no operational counterpart.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>How to read a cell</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="39" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="B12" s="28" t="inlineStr">
+    <row r="13" ht="39" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>GRANTED. This role holds an explicit grant for this feature in public/config/personas.json. The "Levels granted" column shows which permission levels appear across roles; per-role level detail is in that file.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="27" t="inlineStr">
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>(blank)</t>
         </is>
       </c>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>NOT GRANTED — a decision, not a gap. Grants are exhaustive for the 26 roles, so an empty cell means this role was deliberately not given the feature. NOTE: this INVERTS the previous edition of this workbook, where a tick required an rbac.json evidence row and a blank meant "the source corpus never said". That model was retired on 2026-09-24.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="39" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
+    <row r="15" ht="39" customHeight="1">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>Status = Planned</t>
         </is>
       </c>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>The feature is granted and navigable, but none of its screens is registered in the app yet, so it renders as a visible placeholder. This is deliberate: a granted-but-unbuilt feature stays visible to indicate planned functionality rather than disappearing.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Approach</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="27" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>Customer-First</t>
         </is>
       </c>
-      <c r="B17" s="28" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>15 roles. Drives customer-centric navigation, landing zone and search scope.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="27" t="inlineStr">
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>Product-First</t>
         </is>
       </c>
-      <c r="B18" s="28" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>5 roles. Work-item-first: the landing zone shows the role's own work queues (fulfilment, dispatch, catalog administration) rather than a customer list.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="27" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="B19" s="28" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>5 roles. Both zones, with a Focus control to re-order and re-size them.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="27" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="B20" s="28" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>1 role (View Only). Read-only treatment, no approach-specific landing experience.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t>Credentials</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="27" t="inlineStr">
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>Staff IDs</t>
         </is>
       </c>
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>VFQ12341–VFQ12366, one per role, all sign-in-able. Entry is normalised: "VFQ-12341", "vfq 12341" and "VFQ12341" all resolve to the same role.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="39" customHeight="1">
-      <c r="A24" s="27" t="inlineStr">
+    <row r="25" ht="39" customHeight="1">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>Password</t>
         </is>
       </c>
-      <c r="B24" s="28" t="inlineStr">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>"Vodafone@123" — one shared placeholder demo credential for every role, parsed from src/auth/staffIdRoleMap.ts when this workbook was generated. The real IDAM policy and credential source remain open items (D-02, OI-AGN-04). Not a real credential scheme; do not treat it as one.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="39" customHeight="1">
-      <c r="A25" s="27" t="inlineStr">
+    <row r="26" ht="39" customHeight="1">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B25" s="28" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>Each role names its own seeded identity via identityUserId, so a Staff ID always resolves to the same agent name / job title / team. Replaced a keyword matcher that collapsed every manager role onto one identity.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="26" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="52" customHeight="1">
-      <c r="A28" s="27" t="inlineStr">
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>Roles</t>
         </is>
       </c>
-      <c r="B28" s="28" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>26. Rows 1–25 are the VFQ operational role table as supplied; ROLE-26 (Complaints Agent) was added to own ticket resolution, since the table has no Complaints Team successor and widening resolution to every care agent would have discarded the documented raise-vs-resolve separation (BR-067 / RBAC-132).</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="27" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="B29" s="28" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>47 catalogued (34 built, 13 planned).</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="27" t="inlineStr">
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>Screens</t>
         </is>
       </c>
-      <c r="B30" s="28" t="inlineStr">
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>69 of 213 catalogued screens are registered in the app. Features whose screens are all unregistered show as Planned rather than being omitted.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="27" t="inlineStr">
+    <row r="32" ht="65" customHeight="1">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>Superseded sources</t>
         </is>
       </c>
-      <c r="B31" s="28" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>These now-duplicate persona records should be treated as historical, not authoritative: VFQ_DXP_Personas_Reference.xlsx "Personas" (the 66-persona model), VFQ_DXP_Test_Data_Reference.xlsx "Login Credentials" (7 old Staff IDs with role labels that have since changed meaning), and the same workbook's "Persona" and "Persona by Approach" sheets. The 66-persona model and its RBAC evidence are archived under reference/blueprint/legacy/.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="26" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>Keeping this file the SSOT</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="27" t="inlineStr">
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>1. Edit the source, not the file</t>
         </is>
       </c>
-      <c r="B34" s="28" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>Roles, grants, capabilities and credentials all live in public/config/personas.json and public/config/feature-catalogue.json.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="27" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t>2. Regenerate</t>
         </is>
       </c>
-      <c r="B35" s="28" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>python3 reference/scripts/build_persona_feature_matrix.py</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="27" t="inlineStr">
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t>3. Never hand-edit the .xlsx</t>
         </is>
       </c>
-      <c r="B36" s="28" t="inlineStr">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>The next regeneration overwrites it. The script is the source; the workbook is the artefact. (Opening it in Excel and saving will also silently rewrite it.)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="52" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
+    <row r="38" ht="52" customHeight="1">
+      <c r="A38" s="29" t="inlineStr">
         <is>
           <t>Drift guards</t>
         </is>
       </c>
-      <c r="B37" s="28" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>The script aborts rather than emit a misleading workbook if: a capability is gated in code or granted in personas.json but missing from the PersonaCapability union; a grant references an unknown feature key or level; a catalogue entry references a screen absent from routes.json; a Staff ID or role id is duplicated; or a role binds an identity absent from users-agents.json.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="29" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="31" t="inlineStr">
         <is>
           <t>Generated from commit</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>4cd4ba5</t>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>252c833</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +68,15 @@
     </font>
     <font>
       <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
       <sz val="8"/>
     </font>
     <font>
@@ -148,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -223,16 +232,21 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9342,7 +9356,7 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Capabilities are in-surface ACTION gates, distinct from the feature grants on the Applicability Matrix sheet: a feature key exists for every navigable surface, a capability for every action gate inside one. Enforced by src/engines/agentPrivilegeEngine.ts.</t>
+          <t>Capabilities are in-surface ACTION gates, distinct from the feature grants on the Applicability Matrix sheet: a feature key exists for every surface carrying its own access decision, a capability for every action gate inside one. Enforced by src/engines/agentPrivilegeEngine.ts.</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y32"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -13148,7 +13162,6 @@
     <col width="5.5" customWidth="1" min="22" max="22"/>
     <col width="5.5" customWidth="1" min="23" max="23"/>
     <col width="5.5" customWidth="1" min="24" max="24"/>
-    <col width="5.5" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="150" customHeight="1">
@@ -13189,90 +13202,85 @@
       </c>
       <c r="H1" s="13" t="inlineStr">
         <is>
-          <t>Customers</t>
+          <t>Customer Search</t>
         </is>
       </c>
       <c r="I1" s="13" t="inlineStr">
         <is>
-          <t>Customer Search</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="J1" s="13" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="K1" s="13" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Leads</t>
         </is>
       </c>
       <c r="L1" s="13" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="M1" s="13" t="inlineStr">
         <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>Administration</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>New Connections</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>Existing Service</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>Number Services</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>SIM &amp; Device</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="N1" s="13" t="inlineStr">
-        <is>
-          <t>Orders</t>
-        </is>
-      </c>
-      <c r="O1" s="13" t="inlineStr">
-        <is>
-          <t>Administration</t>
-        </is>
-      </c>
-      <c r="P1" s="13" t="inlineStr">
+      <c r="T1" s="13" t="inlineStr">
         <is>
           <t>New Connections</t>
         </is>
       </c>
-      <c r="Q1" s="13" t="inlineStr">
+      <c r="U1" s="13" t="inlineStr">
         <is>
           <t>Existing Service</t>
         </is>
       </c>
-      <c r="R1" s="13" t="inlineStr">
-        <is>
-          <t>Number Services</t>
-        </is>
-      </c>
-      <c r="S1" s="13" t="inlineStr">
-        <is>
-          <t>SIM &amp; Device</t>
-        </is>
-      </c>
-      <c r="T1" s="13" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="U1" s="13" t="inlineStr">
-        <is>
-          <t>New Connections</t>
-        </is>
-      </c>
       <c r="V1" s="13" t="inlineStr">
         <is>
-          <t>Existing Service</t>
+          <t>Relocation</t>
         </is>
       </c>
       <c r="W1" s="13" t="inlineStr">
         <is>
-          <t>Relocation</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="X1" s="13" t="inlineStr">
-        <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="Y1" s="13" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
@@ -13300,237 +13308,219 @@
       </c>
       <c r="H2" s="25" t="inlineStr">
         <is>
-          <t>customers</t>
+          <t>customer-search</t>
         </is>
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>customer-search</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="J2" s="25" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>operations</t>
         </is>
       </c>
       <c r="K2" s="25" t="inlineStr">
         <is>
-          <t>operations</t>
+          <t>leads</t>
         </is>
       </c>
       <c r="L2" s="25" t="inlineStr">
         <is>
-          <t>leads</t>
+          <t>support</t>
         </is>
       </c>
       <c r="M2" s="25" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="N2" s="25" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>administration</t>
         </is>
       </c>
       <c r="O2" s="25" t="inlineStr">
         <is>
-          <t>administration</t>
+          <t>mobile.new-connections</t>
         </is>
       </c>
       <c r="P2" s="25" t="inlineStr">
         <is>
-          <t>mobile.new-connections</t>
+          <t>mobile.existing-service</t>
         </is>
       </c>
       <c r="Q2" s="25" t="inlineStr">
         <is>
-          <t>mobile.existing-service</t>
+          <t>mobile.number-services</t>
         </is>
       </c>
       <c r="R2" s="25" t="inlineStr">
         <is>
-          <t>mobile.number-services</t>
+          <t>mobile.sim-device</t>
         </is>
       </c>
       <c r="S2" s="25" t="inlineStr">
         <is>
-          <t>mobile.sim-device</t>
+          <t>mobile.support</t>
         </is>
       </c>
       <c r="T2" s="25" t="inlineStr">
         <is>
-          <t>mobile.support</t>
+          <t>fibre-home.new-connections</t>
         </is>
       </c>
       <c r="U2" s="25" t="inlineStr">
         <is>
-          <t>fibre-home.new-connections</t>
+          <t>fibre-home.existing-service</t>
         </is>
       </c>
       <c r="V2" s="25" t="inlineStr">
         <is>
-          <t>fibre-home.existing-service</t>
+          <t>fibre-home.relocation</t>
         </is>
       </c>
       <c r="W2" s="25" t="inlineStr">
         <is>
-          <t>fibre-home.relocation</t>
+          <t>fibre-home.equipment</t>
         </is>
       </c>
       <c r="X2" s="25" t="inlineStr">
         <is>
-          <t>fibre-home.equipment</t>
-        </is>
-      </c>
-      <c r="Y2" s="25" t="inlineStr">
-        <is>
           <t>fibre-home.support</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>ROLE-01</t>
-        </is>
-      </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>VFQ12341</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Retail Sales Agent</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O3" s="21" t="n"/>
-      <c r="P3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y3" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
+    <row r="3" ht="120" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>governed by →</t>
+        </is>
+      </c>
+      <c r="B3" s="27" t="n"/>
+      <c r="C3" s="27" t="n"/>
+      <c r="D3" s="27" t="n"/>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>approach ordering (IA only)</t>
+        </is>
+      </c>
+      <c r="F3" s="28" t="inlineStr">
+        <is>
+          <t>approach (always shown); categories gated by journey grants</t>
+        </is>
+      </c>
+      <c r="G3" s="28" t="inlineStr">
+        <is>
+          <t>approach (always shown); categories gated by journey grants</t>
+        </is>
+      </c>
+      <c r="H3" s="28" t="inlineStr">
+        <is>
+          <t>approach ordering (IA only)</t>
+        </is>
+      </c>
+      <c r="I3" s="28" t="inlineStr">
+        <is>
+          <t>approach ordering (IA only)</t>
+        </is>
+      </c>
+      <c r="J3" s="28" t="inlineStr">
+        <is>
+          <t>approach ordering (IA only)</t>
+        </is>
+      </c>
+      <c r="K3" s="28" t="inlineStr">
+        <is>
+          <t>approach ordering (IA only)</t>
+        </is>
+      </c>
+      <c r="L3" s="28" t="inlineStr">
+        <is>
+          <t>approach ordering (IA only)</t>
+        </is>
+      </c>
+      <c r="M3" s="28" t="inlineStr">
+        <is>
+          <t>approach ordering (IA only)</t>
+        </is>
+      </c>
+      <c r="N3" s="28" t="inlineStr">
+        <is>
+          <t>feature grant: workspace.admin-role-access-viewer</t>
+        </is>
+      </c>
+      <c r="O3" s="28" t="inlineStr">
+        <is>
+          <t>journey grants in this category</t>
+        </is>
+      </c>
+      <c r="P3" s="28" t="inlineStr">
+        <is>
+          <t>journey grants in this category</t>
+        </is>
+      </c>
+      <c r="Q3" s="28" t="inlineStr">
+        <is>
+          <t>journey grants in this category</t>
+        </is>
+      </c>
+      <c r="R3" s="28" t="inlineStr">
+        <is>
+          <t>journey grants in this category</t>
+        </is>
+      </c>
+      <c r="S3" s="28" t="inlineStr">
+        <is>
+          <t>journey grants in this category</t>
+        </is>
+      </c>
+      <c r="T3" s="28" t="inlineStr">
+        <is>
+          <t>journey grants in this category</t>
+        </is>
+      </c>
+      <c r="U3" s="28" t="inlineStr">
+        <is>
+          <t>journey grants in this category</t>
+        </is>
+      </c>
+      <c r="V3" s="28" t="inlineStr">
+        <is>
+          <t>journey grants in this category</t>
+        </is>
+      </c>
+      <c r="W3" s="28" t="inlineStr">
+        <is>
+          <t>journey grants in this category</t>
+        </is>
+      </c>
+      <c r="X3" s="28" t="inlineStr">
+        <is>
+          <t>journey grants in this category</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="23" t="inlineStr">
         <is>
-          <t>ROLE-02</t>
+          <t>ROLE-01</t>
         </is>
       </c>
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t>VFQ12342</t>
+          <t>VFQ12341</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Telesales Agent</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Customer-First</t>
+          <t>Retail Sales Agent</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E4" s="20" t="inlineStr">
@@ -13538,9 +13528,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F4" s="21" t="n"/>
-      <c r="G4" s="21" t="n"/>
-      <c r="H4" s="21" t="n"/>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I4" s="20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -13551,44 +13553,87 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K4" s="21" t="n"/>
-      <c r="L4" s="21" t="n"/>
+      <c r="K4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M4" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N4" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O4" s="21" t="n"/>
-      <c r="P4" s="21" t="n"/>
-      <c r="Q4" s="21" t="n"/>
-      <c r="R4" s="21" t="n"/>
-      <c r="S4" s="21" t="n"/>
-      <c r="T4" s="21" t="n"/>
-      <c r="U4" s="21" t="n"/>
-      <c r="V4" s="21" t="n"/>
-      <c r="W4" s="21" t="n"/>
-      <c r="X4" s="21" t="n"/>
-      <c r="Y4" s="21" t="n"/>
+      <c r="N4" s="21" t="n"/>
+      <c r="O4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X4" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>ROLE-03</t>
+          <t>ROLE-02</t>
         </is>
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>VFQ12343</t>
+          <t>VFQ12342</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Direct Sales Agent</t>
+          <t>Telesales Agent</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -13603,29 +13648,29 @@
       </c>
       <c r="F5" s="21" t="n"/>
       <c r="G5" s="21" t="n"/>
-      <c r="H5" s="21" t="n"/>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J5" s="21" t="n"/>
       <c r="K5" s="21" t="n"/>
-      <c r="L5" s="21" t="n"/>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M5" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N5" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N5" s="21" t="n"/>
       <c r="O5" s="21" t="n"/>
       <c r="P5" s="21" t="n"/>
       <c r="Q5" s="21" t="n"/>
@@ -13636,22 +13681,21 @@
       <c r="V5" s="21" t="n"/>
       <c r="W5" s="21" t="n"/>
       <c r="X5" s="21" t="n"/>
-      <c r="Y5" s="21" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="23" t="inlineStr">
         <is>
-          <t>ROLE-04</t>
+          <t>ROLE-03</t>
         </is>
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>VFQ12344</t>
+          <t>VFQ12343</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Tablet / Field Sales Agent</t>
+          <t>Direct Sales Agent</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -13666,29 +13710,29 @@
       </c>
       <c r="F6" s="21" t="n"/>
       <c r="G6" s="21" t="n"/>
-      <c r="H6" s="21" t="n"/>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J6" s="21" t="n"/>
       <c r="K6" s="21" t="n"/>
-      <c r="L6" s="21" t="n"/>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M6" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N6" s="21" t="n"/>
       <c r="O6" s="21" t="n"/>
       <c r="P6" s="21" t="n"/>
       <c r="Q6" s="21" t="n"/>
@@ -13699,22 +13743,21 @@
       <c r="V6" s="21" t="n"/>
       <c r="W6" s="21" t="n"/>
       <c r="X6" s="21" t="n"/>
-      <c r="Y6" s="21" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>ROLE-05</t>
+          <t>ROLE-04</t>
         </is>
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>VFQ12345</t>
+          <t>VFQ12344</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Mass Market Agent</t>
+          <t>Tablet / Field Sales Agent</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -13729,29 +13772,29 @@
       </c>
       <c r="F7" s="21" t="n"/>
       <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J7" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J7" s="21" t="n"/>
       <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M7" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N7" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N7" s="21" t="n"/>
       <c r="O7" s="21" t="n"/>
       <c r="P7" s="21" t="n"/>
       <c r="Q7" s="21" t="n"/>
@@ -13762,22 +13805,21 @@
       <c r="V7" s="21" t="n"/>
       <c r="W7" s="21" t="n"/>
       <c r="X7" s="21" t="n"/>
-      <c r="Y7" s="21" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>ROLE-06</t>
+          <t>ROLE-05</t>
         </is>
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>VFQ12346</t>
+          <t>VFQ12345</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Account Manager</t>
+          <t>Mass Market Agent</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -13792,29 +13834,29 @@
       </c>
       <c r="F8" s="21" t="n"/>
       <c r="G8" s="21" t="n"/>
-      <c r="H8" s="21" t="n"/>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I8" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J8" s="21" t="n"/>
       <c r="K8" s="21" t="n"/>
-      <c r="L8" s="21" t="n"/>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M8" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N8" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N8" s="21" t="n"/>
       <c r="O8" s="21" t="n"/>
       <c r="P8" s="21" t="n"/>
       <c r="Q8" s="21" t="n"/>
@@ -13825,22 +13867,21 @@
       <c r="V8" s="21" t="n"/>
       <c r="W8" s="21" t="n"/>
       <c r="X8" s="21" t="n"/>
-      <c r="Y8" s="21" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>ROLE-07</t>
+          <t>ROLE-06</t>
         </is>
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>VFQ12347</t>
+          <t>VFQ12346</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Key Accounts Manager</t>
+          <t>Account Manager</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -13855,29 +13896,29 @@
       </c>
       <c r="F9" s="21" t="n"/>
       <c r="G9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J9" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J9" s="21" t="n"/>
       <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M9" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N9" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N9" s="21" t="n"/>
       <c r="O9" s="21" t="n"/>
       <c r="P9" s="21" t="n"/>
       <c r="Q9" s="21" t="n"/>
@@ -13888,27 +13929,26 @@
       <c r="V9" s="21" t="n"/>
       <c r="W9" s="21" t="n"/>
       <c r="X9" s="21" t="n"/>
-      <c r="Y9" s="21" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>ROLE-08</t>
+          <t>ROLE-07</t>
         </is>
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>VFQ12348</t>
+          <t>VFQ12347</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Channel Manager</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
+          <t>Key Accounts Manager</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -13916,16 +13956,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="21" t="n"/>
       <c r="H10" s="20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -13936,16 +13968,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K10" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="21" t="n"/>
       <c r="L10" s="20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -13956,58 +13980,37 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N10" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N10" s="21" t="n"/>
       <c r="O10" s="21" t="n"/>
       <c r="P10" s="21" t="n"/>
-      <c r="Q10" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q10" s="21" t="n"/>
       <c r="R10" s="21" t="n"/>
       <c r="S10" s="21" t="n"/>
-      <c r="T10" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T10" s="21" t="n"/>
       <c r="U10" s="21" t="n"/>
-      <c r="V10" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="V10" s="21" t="n"/>
       <c r="W10" s="21" t="n"/>
-      <c r="X10" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y10" s="21" t="n"/>
+      <c r="X10" s="21" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>ROLE-09</t>
+          <t>ROLE-08</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>VFQ12349</t>
+          <t>VFQ12348</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Authorized Officer</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Customer-First</t>
+          <t>Channel Manager</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -14015,9 +14018,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F11" s="21" t="n"/>
-      <c r="G11" s="21" t="n"/>
-      <c r="H11" s="21" t="n"/>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -14028,44 +14043,63 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="21" t="n"/>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M11" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N11" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N11" s="21" t="n"/>
       <c r="O11" s="21" t="n"/>
-      <c r="P11" s="21" t="n"/>
+      <c r="P11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q11" s="21" t="n"/>
       <c r="R11" s="21" t="n"/>
-      <c r="S11" s="21" t="n"/>
+      <c r="S11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T11" s="21" t="n"/>
-      <c r="U11" s="21" t="n"/>
+      <c r="U11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V11" s="21" t="n"/>
-      <c r="W11" s="21" t="n"/>
+      <c r="W11" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="X11" s="21" t="n"/>
-      <c r="Y11" s="21" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>ROLE-10</t>
+          <t>ROLE-09</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>VFQ12350</t>
+          <t>VFQ12349</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Customer Care Agent</t>
+          <t>Authorized Officer</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -14080,29 +14114,29 @@
       </c>
       <c r="F12" s="21" t="n"/>
       <c r="G12" s="21" t="n"/>
-      <c r="H12" s="21" t="n"/>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J12" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J12" s="21" t="n"/>
       <c r="K12" s="21" t="n"/>
-      <c r="L12" s="21" t="n"/>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M12" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N12" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N12" s="21" t="n"/>
       <c r="O12" s="21" t="n"/>
       <c r="P12" s="21" t="n"/>
       <c r="Q12" s="21" t="n"/>
@@ -14113,22 +14147,21 @@
       <c r="V12" s="21" t="n"/>
       <c r="W12" s="21" t="n"/>
       <c r="X12" s="21" t="n"/>
-      <c r="Y12" s="21" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>ROLE-11</t>
+          <t>ROLE-10</t>
         </is>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>VFQ12351</t>
+          <t>VFQ12350</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Business Care Agent</t>
+          <t>Customer Care Agent</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -14143,29 +14176,29 @@
       </c>
       <c r="F13" s="21" t="n"/>
       <c r="G13" s="21" t="n"/>
-      <c r="H13" s="21" t="n"/>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J13" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J13" s="21" t="n"/>
       <c r="K13" s="21" t="n"/>
-      <c r="L13" s="21" t="n"/>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M13" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N13" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N13" s="21" t="n"/>
       <c r="O13" s="21" t="n"/>
       <c r="P13" s="21" t="n"/>
       <c r="Q13" s="21" t="n"/>
@@ -14176,22 +14209,21 @@
       <c r="V13" s="21" t="n"/>
       <c r="W13" s="21" t="n"/>
       <c r="X13" s="21" t="n"/>
-      <c r="Y13" s="21" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>ROLE-12</t>
+          <t>ROLE-11</t>
         </is>
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>VFQ12352</t>
+          <t>VFQ12351</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Premium Agent</t>
+          <t>Business Care Agent</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -14206,29 +14238,29 @@
       </c>
       <c r="F14" s="21" t="n"/>
       <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J14" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J14" s="21" t="n"/>
       <c r="K14" s="21" t="n"/>
-      <c r="L14" s="21" t="n"/>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M14" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N14" s="21" t="n"/>
       <c r="O14" s="21" t="n"/>
       <c r="P14" s="21" t="n"/>
       <c r="Q14" s="21" t="n"/>
@@ -14239,22 +14271,21 @@
       <c r="V14" s="21" t="n"/>
       <c r="W14" s="21" t="n"/>
       <c r="X14" s="21" t="n"/>
-      <c r="Y14" s="21" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>ROLE-13</t>
+          <t>ROLE-12</t>
         </is>
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>VFQ12353</t>
+          <t>VFQ12352</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Retention Agent</t>
+          <t>Premium Agent</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -14269,29 +14300,29 @@
       </c>
       <c r="F15" s="21" t="n"/>
       <c r="G15" s="21" t="n"/>
-      <c r="H15" s="21" t="n"/>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J15" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J15" s="21" t="n"/>
       <c r="K15" s="21" t="n"/>
-      <c r="L15" s="21" t="n"/>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M15" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N15" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N15" s="21" t="n"/>
       <c r="O15" s="21" t="n"/>
       <c r="P15" s="21" t="n"/>
       <c r="Q15" s="21" t="n"/>
@@ -14302,27 +14333,26 @@
       <c r="V15" s="21" t="n"/>
       <c r="W15" s="21" t="n"/>
       <c r="X15" s="21" t="n"/>
-      <c r="Y15" s="21" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="23" t="inlineStr">
         <is>
-          <t>ROLE-14</t>
+          <t>ROLE-13</t>
         </is>
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>VFQ12354</t>
+          <t>VFQ12353</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Fulfilment Agent</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Product-First</t>
+          <t>Retention Agent</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -14330,85 +14360,56 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F16" s="21" t="n"/>
+      <c r="G16" s="21" t="n"/>
       <c r="H16" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I16" s="21" t="n"/>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J16" s="21" t="n"/>
-      <c r="K16" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K16" s="21" t="n"/>
       <c r="L16" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M16" s="21" t="n"/>
+      <c r="M16" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N16" s="21" t="n"/>
       <c r="O16" s="21" t="n"/>
       <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q16" s="21" t="n"/>
       <c r="R16" s="21" t="n"/>
-      <c r="S16" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T16" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S16" s="21" t="n"/>
+      <c r="T16" s="21" t="n"/>
       <c r="U16" s="21" t="n"/>
-      <c r="V16" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W16" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X16" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y16" s="21" t="n"/>
+      <c r="V16" s="21" t="n"/>
+      <c r="W16" s="21" t="n"/>
+      <c r="X16" s="21" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>ROLE-15</t>
+          <t>ROLE-14</t>
         </is>
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>VFQ12355</t>
+          <t>VFQ12354</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Back Office Fulfilment Agent</t>
+          <t>Fulfilment Agent</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -14431,76 +14432,75 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H17" s="21" t="n"/>
       <c r="I17" s="21" t="n"/>
-      <c r="J17" s="21" t="n"/>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K17" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L17" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L17" s="21" t="n"/>
       <c r="M17" s="21" t="n"/>
       <c r="N17" s="21" t="n"/>
       <c r="O17" s="21" t="n"/>
-      <c r="P17" s="21" t="n"/>
-      <c r="Q17" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="21" t="n"/>
+      <c r="P17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q17" s="21" t="n"/>
+      <c r="R17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S17" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="T17" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="21" t="n"/>
+      <c r="T17" s="21" t="n"/>
+      <c r="U17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V17" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W17" s="21" t="n"/>
-      <c r="X17" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y17" s="21" t="n"/>
+      <c r="W17" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X17" s="21" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>ROLE-16</t>
+          <t>ROLE-15</t>
         </is>
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>VFQ12356</t>
+          <t>VFQ12355</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>CDM Agent (Customer Data Management Agent)</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Customer-First</t>
+          <t>Back Office Fulfilment Agent</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Product-First</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -14508,62 +14508,81 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F18" s="21" t="n"/>
-      <c r="G18" s="21" t="n"/>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H18" s="21" t="n"/>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I18" s="21" t="n"/>
       <c r="J18" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="K18" s="21" t="n"/>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L18" s="21" t="n"/>
-      <c r="M18" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N18" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M18" s="21" t="n"/>
+      <c r="N18" s="21" t="n"/>
       <c r="O18" s="21" t="n"/>
-      <c r="P18" s="21" t="n"/>
+      <c r="P18" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q18" s="21" t="n"/>
-      <c r="R18" s="21" t="n"/>
-      <c r="S18" s="21" t="n"/>
+      <c r="R18" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T18" s="21" t="n"/>
-      <c r="U18" s="21" t="n"/>
+      <c r="U18" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V18" s="21" t="n"/>
-      <c r="W18" s="21" t="n"/>
+      <c r="W18" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="X18" s="21" t="n"/>
-      <c r="Y18" s="21" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>ROLE-17</t>
+          <t>ROLE-16</t>
         </is>
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>VFQ12357</t>
+          <t>VFQ12356</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>MNP Agent (Mobile Number Portability Agent)</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
+          <t>CDM Agent (Customer Data Management Agent)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -14571,16 +14590,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="21" t="n"/>
       <c r="H19" s="20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -14591,16 +14602,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J19" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K19" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J19" s="21" t="n"/>
+      <c r="K19" s="21" t="n"/>
       <c r="L19" s="20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -14611,74 +14614,37 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N19" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N19" s="21" t="n"/>
       <c r="O19" s="21" t="n"/>
-      <c r="P19" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q19" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T19" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P19" s="21" t="n"/>
+      <c r="Q19" s="21" t="n"/>
+      <c r="R19" s="21" t="n"/>
+      <c r="S19" s="21" t="n"/>
+      <c r="T19" s="21" t="n"/>
       <c r="U19" s="21" t="n"/>
-      <c r="V19" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="V19" s="21" t="n"/>
       <c r="W19" s="21" t="n"/>
-      <c r="X19" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y19" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="X19" s="21" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
         <is>
-          <t>ROLE-18</t>
+          <t>ROLE-17</t>
         </is>
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>VFQ12358</t>
+          <t>VFQ12357</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Billing Agent</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Customer-First</t>
+          <t>MNP Agent (Mobile Number Portability Agent)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -14686,9 +14652,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F20" s="21" t="n"/>
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="21" t="n"/>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -14699,44 +14677,79 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K20" s="21" t="n"/>
-      <c r="L20" s="21" t="n"/>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M20" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N20" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O20" s="21" t="n"/>
-      <c r="P20" s="21" t="n"/>
-      <c r="Q20" s="21" t="n"/>
-      <c r="R20" s="21" t="n"/>
-      <c r="S20" s="21" t="n"/>
+      <c r="N20" s="21" t="n"/>
+      <c r="O20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T20" s="21" t="n"/>
-      <c r="U20" s="21" t="n"/>
+      <c r="U20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V20" s="21" t="n"/>
-      <c r="W20" s="21" t="n"/>
-      <c r="X20" s="21" t="n"/>
-      <c r="Y20" s="21" t="n"/>
+      <c r="W20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X20" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>ROLE-19</t>
+          <t>ROLE-18</t>
         </is>
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>VFQ12359</t>
+          <t>VFQ12358</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Credit Control Agent</t>
+          <t>Billing Agent</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -14751,29 +14764,29 @@
       </c>
       <c r="F21" s="21" t="n"/>
       <c r="G21" s="21" t="n"/>
-      <c r="H21" s="21" t="n"/>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J21" s="21" t="n"/>
       <c r="K21" s="21" t="n"/>
-      <c r="L21" s="21" t="n"/>
+      <c r="L21" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M21" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="N21" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N21" s="21" t="n"/>
       <c r="O21" s="21" t="n"/>
       <c r="P21" s="21" t="n"/>
       <c r="Q21" s="21" t="n"/>
@@ -14784,27 +14797,26 @@
       <c r="V21" s="21" t="n"/>
       <c r="W21" s="21" t="n"/>
       <c r="X21" s="21" t="n"/>
-      <c r="Y21" s="21" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>ROLE-20</t>
+          <t>ROLE-19</t>
         </is>
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>VFQ12360</t>
+          <t>VFQ12359</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Dispatcher</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Product-First</t>
+          <t>Credit Control Agent</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -14812,34 +14824,30 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F22" s="21" t="n"/>
+      <c r="G22" s="21" t="n"/>
       <c r="H22" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I22" s="21" t="n"/>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J22" s="21" t="n"/>
-      <c r="K22" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K22" s="21" t="n"/>
       <c r="L22" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M22" s="21" t="n"/>
+      <c r="M22" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N22" s="21" t="n"/>
       <c r="O22" s="21" t="n"/>
       <c r="P22" s="21" t="n"/>
@@ -14848,41 +14856,24 @@
       <c r="S22" s="21" t="n"/>
       <c r="T22" s="21" t="n"/>
       <c r="U22" s="21" t="n"/>
-      <c r="V22" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W22" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X22" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y22" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="V22" s="21" t="n"/>
+      <c r="W22" s="21" t="n"/>
+      <c r="X22" s="21" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>ROLE-21</t>
+          <t>ROLE-20</t>
         </is>
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>VFQ12361</t>
+          <t>VFQ12360</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Field Engineer</t>
+          <t>Dispatcher</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -14905,23 +14896,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H23" s="21" t="n"/>
       <c r="I23" s="21" t="n"/>
-      <c r="J23" s="21" t="n"/>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K23" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L23" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L23" s="21" t="n"/>
       <c r="M23" s="21" t="n"/>
       <c r="N23" s="21" t="n"/>
       <c r="O23" s="21" t="n"/>
@@ -14930,7 +14917,11 @@
       <c r="R23" s="21" t="n"/>
       <c r="S23" s="21" t="n"/>
       <c r="T23" s="21" t="n"/>
-      <c r="U23" s="21" t="n"/>
+      <c r="U23" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V23" s="20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -14942,11 +14933,6 @@
         </is>
       </c>
       <c r="X23" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y23" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -14955,22 +14941,22 @@
     <row r="24">
       <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>ROLE-22</t>
+          <t>ROLE-21</t>
         </is>
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>VFQ12362</t>
+          <t>VFQ12361</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Supervisor</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
+          <t>Field Engineer</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Product-First</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -14988,16 +14974,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="21" t="n"/>
       <c r="J24" s="20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -15008,40 +14986,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L24" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M24" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N24" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O24" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L24" s="21" t="n"/>
+      <c r="M24" s="21" t="n"/>
+      <c r="N24" s="21" t="n"/>
+      <c r="O24" s="21" t="n"/>
       <c r="P24" s="21" t="n"/>
-      <c r="Q24" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q24" s="21" t="n"/>
       <c r="R24" s="21" t="n"/>
       <c r="S24" s="21" t="n"/>
-      <c r="T24" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="21" t="n"/>
+      <c r="T24" s="21" t="n"/>
+      <c r="U24" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V24" s="20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -15053,11 +15011,6 @@
         </is>
       </c>
       <c r="X24" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y24" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -15066,17 +15019,17 @@
     <row r="25">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>ROLE-23</t>
+          <t>ROLE-22</t>
         </is>
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>VFQ12363</t>
+          <t>VFQ12362</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Manager/Approver</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -15134,37 +15087,36 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O25" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P25" s="21" t="n"/>
-      <c r="Q25" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O25" s="21" t="n"/>
+      <c r="P25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q25" s="21" t="n"/>
       <c r="R25" s="21" t="n"/>
-      <c r="S25" s="21" t="n"/>
-      <c r="T25" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="21" t="n"/>
+      <c r="S25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T25" s="21" t="n"/>
+      <c r="U25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V25" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W25" s="21" t="n"/>
+      <c r="W25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="X25" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y25" s="20" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -15173,22 +15125,22 @@
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>ROLE-24</t>
+          <t>ROLE-23</t>
         </is>
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>VFQ12364</t>
+          <t>VFQ12363</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>System Administrator</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>Product-First</t>
+          <t>Manager/Approver</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -15211,8 +15163,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I26" s="21" t="n"/>
-      <c r="J26" s="21" t="n"/>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K26" s="20" t="inlineStr">
         <is>
           <t>✓</t>
@@ -15223,43 +15183,66 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="M26" s="21" t="n"/>
-      <c r="N26" s="21" t="n"/>
-      <c r="O26" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P26" s="21" t="n"/>
+      <c r="M26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O26" s="21" t="n"/>
+      <c r="P26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q26" s="21" t="n"/>
       <c r="R26" s="21" t="n"/>
-      <c r="S26" s="21" t="n"/>
+      <c r="S26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T26" s="21" t="n"/>
-      <c r="U26" s="21" t="n"/>
+      <c r="U26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V26" s="21" t="n"/>
-      <c r="W26" s="21" t="n"/>
-      <c r="X26" s="21" t="n"/>
-      <c r="Y26" s="21" t="n"/>
+      <c r="W26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X26" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>ROLE-25</t>
+          <t>ROLE-24</t>
         </is>
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>VFQ12365</t>
+          <t>VFQ12364</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>View Only</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>System Administrator</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Product-First</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -15267,23 +15250,35 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F27" s="21" t="n"/>
-      <c r="G27" s="21" t="n"/>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H27" s="21" t="n"/>
-      <c r="I27" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J27" s="21" t="n"/>
-      <c r="K27" s="21" t="n"/>
+      <c r="I27" s="21" t="n"/>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L27" s="21" t="n"/>
-      <c r="M27" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N27" s="21" t="n"/>
+      <c r="M27" s="21" t="n"/>
+      <c r="N27" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O27" s="21" t="n"/>
       <c r="P27" s="21" t="n"/>
       <c r="Q27" s="21" t="n"/>
@@ -15294,27 +15289,26 @@
       <c r="V27" s="21" t="n"/>
       <c r="W27" s="21" t="n"/>
       <c r="X27" s="21" t="n"/>
-      <c r="Y27" s="21" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>ROLE-26</t>
+          <t>ROLE-25</t>
         </is>
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>VFQ12366</t>
+          <t>VFQ12365</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Complaints Agent</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Customer-First</t>
+          <t>View Only</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -15324,29 +15318,21 @@
       </c>
       <c r="F28" s="21" t="n"/>
       <c r="G28" s="21" t="n"/>
-      <c r="H28" s="21" t="n"/>
-      <c r="I28" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="n"/>
+      <c r="J28" s="21" t="n"/>
       <c r="K28" s="21" t="n"/>
-      <c r="L28" s="21" t="n"/>
-      <c r="M28" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N28" s="20" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="n"/>
+      <c r="N28" s="21" t="n"/>
       <c r="O28" s="21" t="n"/>
       <c r="P28" s="21" t="n"/>
       <c r="Q28" s="21" t="n"/>
@@ -15357,20 +15343,81 @@
       <c r="V28" s="21" t="n"/>
       <c r="W28" s="21" t="n"/>
       <c r="X28" s="21" t="n"/>
-      <c r="Y28" s="21" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>ROLE-26</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>VFQ12366</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Complaints Agent</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Customer-First</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="21" t="n"/>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="n"/>
+      <c r="K29" s="21" t="n"/>
+      <c r="L29" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M29" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N29" s="21" t="n"/>
+      <c r="O29" s="21" t="n"/>
+      <c r="P29" s="21" t="n"/>
+      <c r="Q29" s="21" t="n"/>
+      <c r="R29" s="21" t="n"/>
+      <c r="S29" s="21" t="n"/>
+      <c r="T29" s="21" t="n"/>
+      <c r="U29" s="21" t="n"/>
+      <c r="V29" s="21" t="n"/>
+      <c r="W29" s="21" t="n"/>
+      <c r="X29" s="21" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>Which primary destinations each role sees in the sidebar. Parsed from src/engines/navigationEngine.ts (approach -&gt; ordered subset), src/navigation/navManifest.ts (the closed set of destinations) and src/navigation/journeyCatalogue.ts (which product-line categories a role can reach) — not restated, so it cannot drift from the running app. Indented keys (mobile.*, fibre-home.*) are journey categories inside a product line; both product lines always appear in the rail even where a role reaches none of their categories.</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32"/>
+    <row r="33"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A30:L32"/>
+    <mergeCell ref="A31:L33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15390,358 +15437,358 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="26" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>VFQ DXP — Roles, Credentials &amp; Feature Applicability</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>SINGLE SOURCE OF TRUTH for the 26 operational roles. Generated from the app source — do not hand-edit.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>Sheets</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>Roles &amp; Credentials</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>The role master: all 26 roles with Staff ID, password, group, business unit, approach, channel, context card, the identity each resolves to at login, capability list and legacy crosswalk. Start here.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>Applicability Matrix</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Feature x role grid. One column per role (row 1 name, row 2 role id + Staff ID, row 3 approach), one row per catalogued feature.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>Capabilities</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Role x action-gate grid. In-surface permissions (resolve a ticket, assign a task, edit customer records) as opposed to "can reach this screen".</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Feature Inventory</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Per feature: key, area, surface, built/planned, screen ids, how many roles hold it, levels granted, and any documented restrictions.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Navigation</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Which sidebar destinations each role sees, including per product-line journey category. Parsed from the navigation source rather than restated, so it cannot drift from the app.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Legacy Crosswalk</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>The 66-persona -&gt; 26-role mapping, including the 17 legacy personas with no operational counterpart.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>How to read a cell</t>
         </is>
       </c>
     </row>
     <row r="13" ht="39" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>GRANTED. This role holds an explicit grant for this feature in public/config/personas.json. The "Levels granted" column shows which permission levels appear across roles; per-role level detail is in that file.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>(blank)</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>NOT GRANTED — a decision, not a gap. Grants are exhaustive for the 26 roles, so an empty cell means this role was deliberately not given the feature. NOTE: this INVERTS the previous edition of this workbook, where a tick required an rbac.json evidence row and a blank meant "the source corpus never said". That model was retired on 2026-09-24.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="39" customHeight="1">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>Status = Planned</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>The feature is granted and navigable, but none of its screens is registered in the app yet, so it renders as a visible placeholder. This is deliberate: a granted-but-unbuilt feature stays visible to indicate planned functionality rather than disappearing.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Approach</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>Customer-First</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>15 roles. Drives customer-centric navigation, landing zone and search scope.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>Product-First</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>5 roles. Work-item-first: the landing zone shows the role's own work queues (fulfilment, dispatch, catalog administration) rather than a customer list.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>5 roles. Both zones, with a Focus control to re-order and re-size them.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>1 role (View Only). Read-only treatment, no approach-specific landing experience.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>Credentials</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>Staff IDs</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>VFQ12341–VFQ12366, one per role, all sign-in-able. Entry is normalised: "VFQ-12341", "vfq 12341" and "VFQ12341" all resolve to the same role.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="39" customHeight="1">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>Password</t>
         </is>
       </c>
-      <c r="B25" s="30" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>"Vodafone@123" — one shared placeholder demo credential for every role, parsed from src/auth/staffIdRoleMap.ts when this workbook was generated. The real IDAM policy and credential source remain open items (D-02, OI-AGN-04). Not a real credential scheme; do not treat it as one.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="39" customHeight="1">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>Each role names its own seeded identity via identityUserId, so a Staff ID always resolves to the same agent name / job title / team. Replaced a keyword matcher that collapsed every manager role onto one identity.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="inlineStr">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
     </row>
     <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>Roles</t>
         </is>
       </c>
-      <c r="B29" s="30" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>26. Rows 1–25 are the VFQ operational role table as supplied; ROLE-26 (Complaints Agent) was added to own ticket resolution, since the table has no Complaints Team successor and widening resolution to every care agent would have discarded the documented raise-vs-resolve separation (BR-067 / RBAC-132).</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>47 catalogued (34 built, 13 planned).</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>Screens</t>
         </is>
       </c>
-      <c r="B31" s="30" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>69 of 213 catalogued screens are registered in the app. Features whose screens are all unregistered show as Planned rather than being omitted.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>Superseded sources</t>
         </is>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>These now-duplicate persona records should be treated as historical, not authoritative: VFQ_DXP_Personas_Reference.xlsx "Personas" (the 66-persona model), VFQ_DXP_Test_Data_Reference.xlsx "Login Credentials" (7 old Staff IDs with role labels that have since changed meaning), and the same workbook's "Persona" and "Persona by Approach" sheets. The 66-persona model and its RBAC evidence are archived under reference/blueprint/legacy/.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="inlineStr">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t>Keeping this file the SSOT</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t>1. Edit the source, not the file</t>
         </is>
       </c>
-      <c r="B35" s="30" t="inlineStr">
+      <c r="B35" s="33" t="inlineStr">
         <is>
           <t>Roles, grants, capabilities and credentials all live in public/config/personas.json and public/config/feature-catalogue.json.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="29" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>2. Regenerate</t>
         </is>
       </c>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>python3 reference/scripts/build_persona_feature_matrix.py</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>3. Never hand-edit the .xlsx</t>
         </is>
       </c>
-      <c r="B37" s="30" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>The next regeneration overwrites it. The script is the source; the workbook is the artefact. (Opening it in Excel and saving will also silently rewrite it.)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="52" customHeight="1">
-      <c r="A38" s="29" t="inlineStr">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>Drift guards</t>
         </is>
       </c>
-      <c r="B38" s="30" t="inlineStr">
+      <c r="B38" s="33" t="inlineStr">
         <is>
           <t>The script aborts rather than emit a misleading workbook if: a capability is gated in code or granted in personas.json but missing from the PersonaCapability union; a grant references an unknown feature key or level; a catalogue entry references a screen absent from routes.json; a Staff ID or role id is duplicated; or a role binds an identity absent from users-agents.json.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="31" t="inlineStr">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>Generated from commit</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>252c833</t>
+          <t>eb8945b</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -13269,12 +13269,12 @@
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>approach (always shown); categories gated by journey grants</t>
+          <t>approach (group always shown); row expands only, does not navigate; categories gated by journey grants</t>
         </is>
       </c>
       <c r="G3" s="28" t="inlineStr">
         <is>
-          <t>approach (always shown); categories gated by journey grants</t>
+          <t>approach (group always shown); row expands only, does not navigate; categories gated by journey grants</t>
         </is>
       </c>
       <c r="H3" s="28" t="inlineStr">
@@ -15649,7 +15649,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>df260ff</t>
+          <t>1efaaa3</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -193,19 +193,19 @@
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom" textRotation="90"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="90" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom" textRotation="90"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="90" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom" textRotation="90"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="90" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom" textRotation="90"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="90" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom" textRotation="90"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="90" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -15290,7 +15290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -15378,278 +15378,290 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1">
+    <row r="10" ht="39" customHeight="1">
       <c r="A10" s="32" t="inlineStr">
         <is>
+          <t>Viewing</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>No sheet has frozen panes — the grids scroll freely, by request. Frozen panes are baked into the file by the generator and would follow it into every viewer and PDF export, so the choice is left to the reader (Excel: View &gt; Freeze Panes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
           <t>Legacy Crosswalk</t>
         </is>
       </c>
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>The 66-persona -&gt; 26-role mapping, including the 17 legacy personas with no operational counterpart.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>How to read a cell</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="39" customHeight="1">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="B13" s="33" t="inlineStr">
+    <row r="14" ht="39" customHeight="1">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>GRANTED. This role holds an explicit grant for this feature in public/config/personas.json. The "Levels granted" column shows which permission levels appear across roles; per-role level detail is in that file.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="32" t="inlineStr">
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>(blank)</t>
         </is>
       </c>
-      <c r="B14" s="33" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>NOT GRANTED — a decision, not a gap. Grants are exhaustive for the 26 roles, so an empty cell means this role was deliberately not given the feature. NOTE: this INVERTS the previous edition of this workbook, where a tick required an rbac.json evidence row and a blank meant "the source corpus never said". That model was retired on 2026-09-24.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="39" customHeight="1">
-      <c r="A15" s="32" t="inlineStr">
+    <row r="16" ht="39" customHeight="1">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>Status = Planned</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>The feature is granted and navigable, but none of its screens is registered in the app yet, so it renders as a visible placeholder. This is deliberate: a granted-but-unbuilt feature stays visible to indicate planned functionality rather than disappearing.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>Approach</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="32" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>Customer-First</t>
         </is>
       </c>
-      <c r="B18" s="33" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>15 roles. Drives customer-centric navigation, landing zone and search scope.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="32" t="inlineStr">
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>Product-First</t>
         </is>
       </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>5 roles. Work-item-first: the landing zone shows the role's own work queues (fulfilment, dispatch, catalog administration) rather than a customer list.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="B20" s="33" t="inlineStr">
-        <is>
-          <t>5 roles. Both zones, with a Focus control to re-order and re-size them.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="32" t="inlineStr">
         <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>5 roles. Both zones, with a Focus control to re-order and re-size them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>1 role (View Only). Read-only treatment, no approach-specific landing experience.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="31" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t>Credentials</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="32" t="inlineStr">
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>Staff IDs</t>
         </is>
       </c>
-      <c r="B24" s="33" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>VFQ12341–VFQ12366, one per role, all sign-in-able. Entry is normalised: "VFQ-12341", "vfq 12341" and "VFQ12341" all resolve to the same role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="39" customHeight="1">
-      <c r="A25" s="32" t="inlineStr">
-        <is>
-          <t>Password</t>
-        </is>
-      </c>
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>"Vodafone@123" — one shared placeholder demo credential for every role, parsed from src/auth/staffIdRoleMap.ts when this workbook was generated. The real IDAM policy and credential source remain open items (D-02, OI-AGN-04). Not a real credential scheme; do not treat it as one.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="39" customHeight="1">
       <c r="A26" s="32" t="inlineStr">
         <is>
+          <t>Password</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>"Vodafone@123" — one shared placeholder demo credential for every role, parsed from src/auth/staffIdRoleMap.ts when this workbook was generated. The real IDAM policy and credential source remain open items (D-02, OI-AGN-04). Not a real credential scheme; do not treat it as one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="39" customHeight="1">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
           <t>Identity</t>
         </is>
       </c>
-      <c r="B26" s="33" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Each role names its own seeded identity via identityUserId, so a Staff ID always resolves to the same agent name / job title / team. Replaced a keyword matcher that collapsed every manager role onto one identity.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="31" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="32" t="inlineStr">
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>Roles</t>
         </is>
       </c>
-      <c r="B29" s="33" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>26. Rows 1–25 are the VFQ operational role table as supplied; ROLE-26 (Complaints Agent) was added to own ticket resolution, since the table has no Complaints Team successor and widening resolution to every care agent would have discarded the documented raise-vs-resolve separation (BR-067 / RBAC-132).</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="32" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="B30" s="33" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>47 catalogued (34 built, 13 planned).</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="32" t="inlineStr">
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>Screens</t>
         </is>
       </c>
-      <c r="B31" s="33" t="inlineStr">
+      <c r="B32" s="33" t="inlineStr">
         <is>
           <t>69 of 213 catalogued screens are registered in the app. Features whose screens are all unregistered show as Planned rather than being omitted.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="32" t="inlineStr">
+    <row r="33" ht="65" customHeight="1">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>Superseded sources</t>
         </is>
       </c>
-      <c r="B32" s="33" t="inlineStr">
+      <c r="B33" s="33" t="inlineStr">
         <is>
           <t>These now-duplicate persona records should be treated as historical, not authoritative: VFQ_DXP_Personas_Reference.xlsx "Personas" (the 66-persona model), VFQ_DXP_Test_Data_Reference.xlsx "Login Credentials" (7 old Staff IDs with role labels that have since changed meaning), and the same workbook's "Persona" and "Persona by Approach" sheets. The 66-persona model and its RBAC evidence are archived under reference/blueprint/legacy/.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="31" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t>Keeping this file the SSOT</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="32" t="inlineStr">
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>1. Edit the source, not the file</t>
         </is>
       </c>
-      <c r="B35" s="33" t="inlineStr">
+      <c r="B36" s="33" t="inlineStr">
         <is>
           <t>Roles, grants, capabilities and credentials all live in public/config/personas.json and public/config/feature-catalogue.json.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="32" t="inlineStr">
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t>2. Regenerate</t>
         </is>
       </c>
-      <c r="B36" s="33" t="inlineStr">
+      <c r="B37" s="33" t="inlineStr">
         <is>
           <t>python3 reference/scripts/build_persona_feature_matrix.py</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="32" t="inlineStr">
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>3. Never hand-edit the .xlsx</t>
         </is>
       </c>
-      <c r="B37" s="33" t="inlineStr">
+      <c r="B38" s="33" t="inlineStr">
         <is>
           <t>The next regeneration overwrites it. The script is the source; the workbook is the artefact. (Opening it in Excel and saving will also silently rewrite it.)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="52" customHeight="1">
-      <c r="A38" s="32" t="inlineStr">
+    <row r="39" ht="52" customHeight="1">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t>Drift guards</t>
         </is>
       </c>
-      <c r="B38" s="33" t="inlineStr">
+      <c r="B39" s="33" t="inlineStr">
         <is>
           <t>The script aborts rather than emit a misleading workbook if: a capability is gated in code or granted in personas.json but missing from the PersonaCapability union; a grant references an unknown feature key or level; a catalogue entry references a screen absent from routes.json; a Staff ID or role id is duplicated; or a role binds an identity absent from users-agents.json.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="34" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="34" t="inlineStr">
         <is>
           <t>Generated from commit</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1efaaa3</t>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>5c19691</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -13269,12 +13269,12 @@
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>approach (group always shown); row expands only, does not navigate; categories gated by journey grants</t>
+          <t>approach (group always shown); row expands only, does not navigate (collapsed rail: hover flyout); categories gated by journey grants</t>
         </is>
       </c>
       <c r="G3" s="28" t="inlineStr">
         <is>
-          <t>approach (group always shown); row expands only, does not navigate; categories gated by journey grants</t>
+          <t>approach (group always shown); row expands only, does not navigate (collapsed rail: hover flyout); categories gated by journey grants</t>
         </is>
       </c>
       <c r="H3" s="28" t="inlineStr">
@@ -15661,7 +15661,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5c19691</t>
+          <t>739b1d0</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="G4" s="18" t="inlineStr">
         <is>
-          <t>Own enterprise account only — INTENT ONLY: no record-level scoping engine exists in this build</t>
+          <t>Own enterprise account only - INTENT ONLY: no record-level scoping engine exists in this build</t>
         </is>
       </c>
       <c r="H4" s="19" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>Own enterprise account only — INTENT ONLY: no record-level scoping engine exists in this build</t>
+          <t>Own enterprise account only - INTENT ONLY: no record-level scoping engine exists in this build</t>
         </is>
       </c>
       <c r="H5" s="19" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>Administration — roles &amp; access viewer</t>
+          <t>Administration - roles &amp; access viewer</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>WFM Activity Details — Admin/Technician view</t>
+          <t>WFM Activity Details - Admin/Technician view</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
-          <t>Cannot set Resolution Code — resolution is owned by the Complaints Agent role</t>
+          <t>Cannot set Resolution Code - resolution is owned by the Complaints Agent role</t>
         </is>
       </c>
       <c r="H38" s="19" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Own enterprise account only — INTENT ONLY: no record-level scoping engine exists in this build</t>
+          <t>Own enterprise account only - INTENT ONLY: no record-level scoping engine exists in this build</t>
         </is>
       </c>
     </row>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Own enterprise account only — INTENT ONLY: no record-level scoping engine exists in this build</t>
+          <t>Own enterprise account only - INTENT ONLY: no record-level scoping engine exists in this build</t>
         </is>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Administration — roles &amp; access viewer</t>
+          <t>Administration - roles &amp; access viewer</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>WFM Activity Details — Admin/Technician view</t>
+          <t>WFM Activity Details - Admin/Technician view</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Cannot set Resolution Code — resolution is owned by the Complaints Agent role</t>
+          <t>Cannot set Resolution Code - resolution is owned by the Complaints Agent role</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>739b1d0</t>
+          <t>c957121</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Roles &amp; Credentials'!$A$1:$S$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Applicability Matrix'!$A$2:$G$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature Inventory'!$A$1:$J$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Applicability Matrix'!$A$2:$G$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Feature Inventory'!$A$1:$J$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Legacy Crosswalk'!$A$1:$D$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="P2" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>65</v>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>55</v>
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q13" s="2" t="n">
         <v>18</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q23" s="2" t="n">
         <v>31</v>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q24" s="2" t="n">
         <v>27</v>
@@ -3122,7 +3122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG49"/>
+  <dimension ref="A1:AG50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4435,12 +4435,12 @@
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Front Desk</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>Task detail</t>
+          <t>My Ticket History (Qnomy)</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="F10" s="18" t="inlineStr">
         <is>
-          <t>Edit, Full</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G10" s="18" t="inlineStr"/>
@@ -4464,102 +4464,34 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I10" s="20" t="n"/>
+      <c r="J10" s="20" t="n"/>
+      <c r="K10" s="20" t="n"/>
       <c r="L10" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M10" s="20" t="n"/>
+      <c r="N10" s="20" t="n"/>
+      <c r="O10" s="20" t="n"/>
       <c r="P10" s="20" t="n"/>
-      <c r="Q10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q10" s="20" t="n"/>
+      <c r="R10" s="20" t="n"/>
       <c r="S10" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="T10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T10" s="20" t="n"/>
+      <c r="U10" s="20" t="n"/>
+      <c r="V10" s="20" t="n"/>
+      <c r="W10" s="20" t="n"/>
+      <c r="X10" s="20" t="n"/>
+      <c r="Y10" s="20" t="n"/>
+      <c r="Z10" s="20" t="n"/>
+      <c r="AA10" s="20" t="n"/>
+      <c r="AB10" s="20" t="n"/>
       <c r="AC10" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -4572,11 +4504,7 @@
       </c>
       <c r="AE10" s="20" t="n"/>
       <c r="AF10" s="20" t="n"/>
-      <c r="AG10" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG10" s="20" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
@@ -4586,12 +4514,12 @@
       </c>
       <c r="B11" s="18" t="inlineStr">
         <is>
-          <t>Agent Profile</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>Agent profile</t>
+          <t>Task detail</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
@@ -4606,7 +4534,7 @@
       </c>
       <c r="F11" s="18" t="inlineStr">
         <is>
-          <t>View, Edit</t>
+          <t>Edit, Full</t>
         </is>
       </c>
       <c r="G11" s="18" t="inlineStr"/>
@@ -4721,16 +4649,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AE11" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF11" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE11" s="20" t="n"/>
+      <c r="AF11" s="20" t="n"/>
       <c r="AG11" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -4745,12 +4665,12 @@
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Agent Profile</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>Administration - roles &amp; access viewer</t>
+          <t>Agent profile</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
@@ -4765,31 +4685,111 @@
       </c>
       <c r="F12" s="18" t="inlineStr">
         <is>
-          <t>View, Full</t>
+          <t>View, Edit</t>
         </is>
       </c>
       <c r="G12" s="18" t="inlineStr"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="20" t="n"/>
-      <c r="K12" s="20" t="n"/>
-      <c r="L12" s="20" t="n"/>
-      <c r="M12" s="20" t="n"/>
-      <c r="N12" s="20" t="n"/>
-      <c r="O12" s="20" t="n"/>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P12" s="20" t="n"/>
-      <c r="Q12" s="20" t="n"/>
-      <c r="R12" s="20" t="n"/>
-      <c r="S12" s="20" t="n"/>
-      <c r="T12" s="20" t="n"/>
-      <c r="U12" s="20" t="n"/>
-      <c r="V12" s="20" t="n"/>
-      <c r="W12" s="20" t="n"/>
-      <c r="X12" s="20" t="n"/>
-      <c r="Y12" s="20" t="n"/>
-      <c r="Z12" s="20" t="n"/>
-      <c r="AA12" s="20" t="n"/>
-      <c r="AB12" s="20" t="n"/>
+      <c r="Q12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AA12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AC12" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -4805,8 +4805,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AF12" s="20" t="n"/>
-      <c r="AG12" s="20" t="n"/>
+      <c r="AF12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AG12" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
@@ -4816,12 +4824,12 @@
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Fixed Line / Fibre</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>New Fixed Line guided wizard</t>
+          <t>Administration - roles &amp; access viewer</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
@@ -4831,32 +4839,20 @@
       </c>
       <c r="E13" s="18" t="inlineStr">
         <is>
-          <t>SCR-043, SCR-045, SCR-046, SCR-048, SCR-050, SCR-058</t>
+          <t>—  (routed directly)</t>
         </is>
       </c>
       <c r="F13" s="18" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>View, Full</t>
         </is>
       </c>
       <c r="G13" s="18" t="inlineStr"/>
-      <c r="H13" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H13" s="20" t="n"/>
       <c r="I13" s="20" t="n"/>
-      <c r="J13" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J13" s="20" t="n"/>
       <c r="K13" s="20" t="n"/>
-      <c r="L13" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L13" s="20" t="n"/>
       <c r="M13" s="20" t="n"/>
       <c r="N13" s="20" t="n"/>
       <c r="O13" s="20" t="n"/>
@@ -4873,9 +4869,21 @@
       <c r="Z13" s="20" t="n"/>
       <c r="AA13" s="20" t="n"/>
       <c r="AB13" s="20" t="n"/>
-      <c r="AC13" s="20" t="n"/>
-      <c r="AD13" s="20" t="n"/>
-      <c r="AE13" s="20" t="n"/>
+      <c r="AC13" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AD13" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE13" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF13" s="20" t="n"/>
       <c r="AG13" s="20" t="n"/>
     </row>
@@ -4892,30 +4900,42 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>WFM Activity Details - Admin/Technician view</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>New Fixed Line guided wizard</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
-          <t>SCR-110</t>
+          <t>SCR-043, SCR-045, SCR-046, SCR-048, SCR-050, SCR-058</t>
         </is>
       </c>
       <c r="F14" s="18" t="inlineStr">
         <is>
-          <t>View, Edit, Full</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="G14" s="18" t="inlineStr"/>
-      <c r="H14" s="20" t="n"/>
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I14" s="20" t="n"/>
-      <c r="J14" s="20" t="n"/>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K14" s="20" t="n"/>
-      <c r="L14" s="20" t="n"/>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M14" s="20" t="n"/>
       <c r="N14" s="20" t="n"/>
       <c r="O14" s="20" t="n"/>
@@ -4924,31 +4944,15 @@
       <c r="R14" s="20" t="n"/>
       <c r="S14" s="20" t="n"/>
       <c r="T14" s="20" t="n"/>
-      <c r="U14" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="U14" s="20" t="n"/>
       <c r="V14" s="20" t="n"/>
       <c r="W14" s="20" t="n"/>
       <c r="X14" s="20" t="n"/>
       <c r="Y14" s="20" t="n"/>
       <c r="Z14" s="20" t="n"/>
-      <c r="AA14" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB14" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AC14" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA14" s="20" t="n"/>
+      <c r="AB14" s="20" t="n"/>
+      <c r="AC14" s="20" t="n"/>
       <c r="AD14" s="20" t="n"/>
       <c r="AE14" s="20" t="n"/>
       <c r="AF14" s="20" t="n"/>
@@ -4962,51 +4966,35 @@
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>FWA / 5G Home</t>
+          <t>Fixed Line / Fibre</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>New FWA / 5G Home guided wizard</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>Built</t>
+          <t>WFM Activity Details - Admin/Technician view</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="E15" s="18" t="inlineStr">
         <is>
-          <t>SCR-077, SCR-078, SCR-079, SCR-080, SCR-082, SCR-084, SCR-085</t>
+          <t>SCR-110</t>
         </is>
       </c>
       <c r="F15" s="18" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>View, Edit, Full</t>
         </is>
       </c>
       <c r="G15" s="18" t="inlineStr"/>
-      <c r="H15" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H15" s="20" t="n"/>
       <c r="I15" s="20" t="n"/>
-      <c r="J15" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K15" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J15" s="20" t="n"/>
+      <c r="K15" s="20" t="n"/>
+      <c r="L15" s="20" t="n"/>
       <c r="M15" s="20" t="n"/>
       <c r="N15" s="20" t="n"/>
       <c r="O15" s="20" t="n"/>
@@ -5015,15 +5003,31 @@
       <c r="R15" s="20" t="n"/>
       <c r="S15" s="20" t="n"/>
       <c r="T15" s="20" t="n"/>
-      <c r="U15" s="20" t="n"/>
+      <c r="U15" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V15" s="20" t="n"/>
       <c r="W15" s="20" t="n"/>
       <c r="X15" s="20" t="n"/>
       <c r="Y15" s="20" t="n"/>
       <c r="Z15" s="20" t="n"/>
-      <c r="AA15" s="20" t="n"/>
-      <c r="AB15" s="20" t="n"/>
-      <c r="AC15" s="20" t="n"/>
+      <c r="AA15" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB15" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC15" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD15" s="20" t="n"/>
       <c r="AE15" s="20" t="n"/>
       <c r="AF15" s="20" t="n"/>
@@ -5042,7 +5046,7 @@
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>Serial number check (Dual Play)</t>
+          <t>New FWA / 5G Home guided wizard</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
@@ -5052,12 +5056,12 @@
       </c>
       <c r="E16" s="18" t="inlineStr">
         <is>
-          <t>SCR-093</t>
+          <t>SCR-077, SCR-078, SCR-079, SCR-080, SCR-082, SCR-084, SCR-085</t>
         </is>
       </c>
       <c r="F16" s="18" t="inlineStr">
         <is>
-          <t>View, Create</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="G16" s="18" t="inlineStr"/>
@@ -5067,13 +5071,21 @@
         </is>
       </c>
       <c r="I16" s="20" t="n"/>
-      <c r="J16" s="20" t="n"/>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K16" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="L16" s="20" t="n"/>
+      <c r="L16" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M16" s="20" t="n"/>
       <c r="N16" s="20" t="n"/>
       <c r="O16" s="20" t="n"/>
@@ -5082,30 +5094,14 @@
       <c r="R16" s="20" t="n"/>
       <c r="S16" s="20" t="n"/>
       <c r="T16" s="20" t="n"/>
-      <c r="U16" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="U16" s="20" t="n"/>
+      <c r="V16" s="20" t="n"/>
       <c r="W16" s="20" t="n"/>
       <c r="X16" s="20" t="n"/>
       <c r="Y16" s="20" t="n"/>
       <c r="Z16" s="20" t="n"/>
-      <c r="AA16" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AB16" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AA16" s="20" t="n"/>
+      <c r="AB16" s="20" t="n"/>
       <c r="AC16" s="20" t="n"/>
       <c r="AD16" s="20" t="n"/>
       <c r="AE16" s="20" t="n"/>
@@ -5125,22 +5121,22 @@
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>Appointment booking &amp; calendar</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>Serial number check (Dual Play)</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="E17" s="18" t="inlineStr">
         <is>
-          <t>SCR-028, SCR-049, SCR-083, SCR-086, SCR-109, SCR-115</t>
+          <t>SCR-093</t>
         </is>
       </c>
       <c r="F17" s="18" t="inlineStr">
         <is>
-          <t>View, Create, Edit, Full</t>
+          <t>View, Create</t>
         </is>
       </c>
       <c r="G17" s="18" t="inlineStr"/>
@@ -5151,7 +5147,11 @@
       </c>
       <c r="I17" s="20" t="n"/>
       <c r="J17" s="20" t="n"/>
-      <c r="K17" s="20" t="n"/>
+      <c r="K17" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L17" s="20" t="n"/>
       <c r="M17" s="20" t="n"/>
       <c r="N17" s="20" t="n"/>
@@ -5166,7 +5166,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V17" s="20" t="n"/>
+      <c r="V17" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W17" s="20" t="n"/>
       <c r="X17" s="20" t="n"/>
       <c r="Y17" s="20" t="n"/>
@@ -5181,11 +5185,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC17" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC17" s="20" t="n"/>
       <c r="AD17" s="20" t="n"/>
       <c r="AE17" s="20" t="n"/>
       <c r="AF17" s="20" t="n"/>
@@ -5199,76 +5199,72 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>Mobile Postpaid</t>
+          <t>FWA / 5G Home</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>New Postpaid Connection wizard</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>Built</t>
+          <t>Appointment booking &amp; calendar</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">
         <is>
-          <t>SCR-037, SCR-154, SCR-155, SCR-156, SCR-157, SCR-158, SCR-159, SCR-160, SCR-161, SCR-162</t>
+          <t>SCR-028, SCR-049, SCR-083, SCR-086, SCR-109, SCR-115</t>
         </is>
       </c>
       <c r="F18" s="18" t="inlineStr">
         <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>Smart Limit / Bill Limit editable only down to the Agent Minimum Value</t>
-        </is>
-      </c>
+          <t>View, Create, Edit, Full</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr"/>
       <c r="H18" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I18" s="20" t="n"/>
       <c r="J18" s="20" t="n"/>
-      <c r="K18" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L18" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="K18" s="20" t="n"/>
+      <c r="L18" s="20" t="n"/>
       <c r="M18" s="20" t="n"/>
       <c r="N18" s="20" t="n"/>
       <c r="O18" s="20" t="n"/>
       <c r="P18" s="20" t="n"/>
       <c r="Q18" s="20" t="n"/>
       <c r="R18" s="20" t="n"/>
-      <c r="S18" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S18" s="20" t="n"/>
       <c r="T18" s="20" t="n"/>
-      <c r="U18" s="20" t="n"/>
+      <c r="U18" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V18" s="20" t="n"/>
       <c r="W18" s="20" t="n"/>
       <c r="X18" s="20" t="n"/>
       <c r="Y18" s="20" t="n"/>
       <c r="Z18" s="20" t="n"/>
-      <c r="AA18" s="20" t="n"/>
-      <c r="AB18" s="20" t="n"/>
-      <c r="AC18" s="20" t="n"/>
+      <c r="AA18" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB18" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AC18" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD18" s="20" t="n"/>
       <c r="AE18" s="20" t="n"/>
       <c r="AF18" s="20" t="n"/>
@@ -5282,12 +5278,12 @@
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>Mobile Prepaid</t>
+          <t>Mobile Postpaid</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>New Prepaid (Tablet) wizard</t>
+          <t>New Postpaid Connection wizard</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
@@ -5297,7 +5293,7 @@
       </c>
       <c r="E19" s="18" t="inlineStr">
         <is>
-          <t>SCR-190, SCR-191, SCR-192</t>
+          <t>SCR-037, SCR-154, SCR-155, SCR-156, SCR-157, SCR-158, SCR-159, SCR-160, SCR-161, SCR-162</t>
         </is>
       </c>
       <c r="F19" s="18" t="inlineStr">
@@ -5305,7 +5301,11 @@
           <t>Create</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr"/>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>Smart Limit / Bill Limit editable only down to the Agent Minimum Value</t>
+        </is>
+      </c>
       <c r="H19" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5333,7 +5333,11 @@
       <c r="P19" s="20" t="n"/>
       <c r="Q19" s="20" t="n"/>
       <c r="R19" s="20" t="n"/>
-      <c r="S19" s="20" t="n"/>
+      <c r="S19" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T19" s="20" t="n"/>
       <c r="U19" s="20" t="n"/>
       <c r="V19" s="20" t="n"/>
@@ -5357,12 +5361,12 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>MNP / FNP Porting</t>
+          <t>Mobile Prepaid</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>MNP process choice gate</t>
+          <t>New Prepaid (Tablet) wizard</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
@@ -5372,12 +5376,12 @@
       </c>
       <c r="E20" s="18" t="inlineStr">
         <is>
-          <t>SCR-120</t>
+          <t>SCR-190, SCR-191, SCR-192</t>
         </is>
       </c>
       <c r="F20" s="18" t="inlineStr">
         <is>
-          <t>View, Create, Full</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="G20" s="18" t="inlineStr"/>
@@ -5392,7 +5396,11 @@
         </is>
       </c>
       <c r="J20" s="20" t="n"/>
-      <c r="K20" s="20" t="n"/>
+      <c r="K20" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L20" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5402,22 +5410,14 @@
       <c r="N20" s="20" t="n"/>
       <c r="O20" s="20" t="n"/>
       <c r="P20" s="20" t="n"/>
-      <c r="Q20" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q20" s="20" t="n"/>
       <c r="R20" s="20" t="n"/>
       <c r="S20" s="20" t="n"/>
       <c r="T20" s="20" t="n"/>
       <c r="U20" s="20" t="n"/>
       <c r="V20" s="20" t="n"/>
       <c r="W20" s="20" t="n"/>
-      <c r="X20" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="X20" s="20" t="n"/>
       <c r="Y20" s="20" t="n"/>
       <c r="Z20" s="20" t="n"/>
       <c r="AA20" s="20" t="n"/>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>MNP Port-In guided wizard</t>
+          <t>MNP process choice gate</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>SCR-121, SCR-122, SCR-123, SCR-124, SCR-125, SCR-126, SCR-127, SCR-129, SCR-132, SCR-133, SCR-134</t>
+          <t>SCR-120</t>
         </is>
       </c>
       <c r="F21" s="18" t="inlineStr">
         <is>
-          <t>Create, Full</t>
+          <t>View, Create, Full</t>
         </is>
       </c>
       <c r="G21" s="18" t="inlineStr"/>
@@ -5481,7 +5481,11 @@
       <c r="N21" s="20" t="n"/>
       <c r="O21" s="20" t="n"/>
       <c r="P21" s="20" t="n"/>
-      <c r="Q21" s="20" t="n"/>
+      <c r="Q21" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R21" s="20" t="n"/>
       <c r="S21" s="20" t="n"/>
       <c r="T21" s="20" t="n"/>
@@ -5511,12 +5515,12 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Lead Management</t>
+          <t>MNP / FNP Porting</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>Lead list views (My / Created / Team / All / Contact)</t>
+          <t>MNP Port-In guided wizard</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
@@ -5526,12 +5530,12 @@
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>SCR-142, SCR-143, SCR-144, SCR-147, SCR-150</t>
+          <t>SCR-121, SCR-122, SCR-123, SCR-124, SCR-125, SCR-126, SCR-127, SCR-129, SCR-132, SCR-133, SCR-134</t>
         </is>
       </c>
       <c r="F22" s="18" t="inlineStr">
         <is>
-          <t>View, Edit</t>
+          <t>Create, Full</t>
         </is>
       </c>
       <c r="G22" s="18" t="inlineStr"/>
@@ -5545,69 +5549,37 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K22" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J22" s="20" t="n"/>
+      <c r="K22" s="20" t="n"/>
       <c r="L22" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M22" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N22" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O22" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M22" s="20" t="n"/>
+      <c r="N22" s="20" t="n"/>
+      <c r="O22" s="20" t="n"/>
       <c r="P22" s="20" t="n"/>
       <c r="Q22" s="20" t="n"/>
       <c r="R22" s="20" t="n"/>
       <c r="S22" s="20" t="n"/>
-      <c r="T22" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T22" s="20" t="n"/>
       <c r="U22" s="20" t="n"/>
       <c r="V22" s="20" t="n"/>
       <c r="W22" s="20" t="n"/>
-      <c r="X22" s="20" t="n"/>
+      <c r="X22" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Y22" s="20" t="n"/>
       <c r="Z22" s="20" t="n"/>
       <c r="AA22" s="20" t="n"/>
       <c r="AB22" s="20" t="n"/>
-      <c r="AC22" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD22" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC22" s="20" t="n"/>
+      <c r="AD22" s="20" t="n"/>
       <c r="AE22" s="20" t="n"/>
-      <c r="AF22" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF22" s="20" t="n"/>
       <c r="AG22" s="20" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
@@ -5623,7 +5595,7 @@
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>Lead detail &amp; lead actions</t>
+          <t>Lead list views (My / Created / Team / All / Contact)</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
@@ -5633,12 +5605,12 @@
       </c>
       <c r="E23" s="18" t="inlineStr">
         <is>
-          <t>SCR-141, SCR-145, SCR-146, SCR-148, SCR-149</t>
+          <t>SCR-142, SCR-143, SCR-144, SCR-147, SCR-150</t>
         </is>
       </c>
       <c r="F23" s="18" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>View, Edit</t>
         </is>
       </c>
       <c r="G23" s="18" t="inlineStr"/>
@@ -5710,7 +5682,11 @@
         </is>
       </c>
       <c r="AE23" s="20" t="n"/>
-      <c r="AF23" s="20" t="n"/>
+      <c r="AF23" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG23" s="20" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -5721,12 +5697,12 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>Order Management</t>
+          <t>Lead Management</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>My Sales Orders queue</t>
+          <t>Lead detail &amp; lead actions</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
@@ -5736,12 +5712,12 @@
       </c>
       <c r="E24" s="18" t="inlineStr">
         <is>
-          <t>SCR-059</t>
+          <t>SCR-141, SCR-145, SCR-146, SCR-148, SCR-149</t>
         </is>
       </c>
       <c r="F24" s="18" t="inlineStr">
         <is>
-          <t>View, Create, Edit</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="G24" s="18" t="inlineStr"/>
@@ -5785,58 +5761,22 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P24" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q24" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P24" s="20" t="n"/>
+      <c r="Q24" s="20" t="n"/>
+      <c r="R24" s="20" t="n"/>
       <c r="S24" s="20" t="n"/>
       <c r="T24" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="U24" s="20" t="n"/>
+      <c r="V24" s="20" t="n"/>
       <c r="W24" s="20" t="n"/>
-      <c r="X24" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y24" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z24" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA24" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="X24" s="20" t="n"/>
+      <c r="Y24" s="20" t="n"/>
+      <c r="Z24" s="20" t="n"/>
+      <c r="AA24" s="20" t="n"/>
       <c r="AB24" s="20" t="n"/>
       <c r="AC24" s="19" t="inlineStr">
         <is>
@@ -5849,16 +5789,8 @@
         </is>
       </c>
       <c r="AE24" s="20" t="n"/>
-      <c r="AF24" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG24" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF24" s="20" t="n"/>
+      <c r="AG24" s="20" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="17" t="inlineStr">
@@ -5873,7 +5805,7 @@
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>Order Approval Queue</t>
+          <t>My Sales Orders queue</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
@@ -5883,25 +5815,45 @@
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>SCR-060, SCR-197</t>
+          <t>SCR-059</t>
         </is>
       </c>
       <c r="F25" s="18" t="inlineStr">
         <is>
-          <t>View, Approve</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>Approve/reject is the only mutating action granted to this otherwise read-only role, per the role table's "approve or reject" wording</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="n"/>
-      <c r="I25" s="20" t="n"/>
-      <c r="J25" s="20" t="n"/>
-      <c r="K25" s="20" t="n"/>
-      <c r="L25" s="20" t="n"/>
-      <c r="M25" s="20" t="n"/>
+          <t>View, Create, Edit</t>
+        </is>
+      </c>
+      <c r="G25" s="18" t="inlineStr"/>
+      <c r="H25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5912,11 +5864,27 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P25" s="20" t="n"/>
-      <c r="Q25" s="20" t="n"/>
-      <c r="R25" s="20" t="n"/>
+      <c r="P25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S25" s="20" t="n"/>
-      <c r="T25" s="20" t="n"/>
+      <c r="T25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U25" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5928,10 +5896,26 @@
         </is>
       </c>
       <c r="W25" s="20" t="n"/>
-      <c r="X25" s="20" t="n"/>
-      <c r="Y25" s="20" t="n"/>
-      <c r="Z25" s="20" t="n"/>
-      <c r="AA25" s="20" t="n"/>
+      <c r="X25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AA25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB25" s="20" t="n"/>
       <c r="AC25" s="19" t="inlineStr">
         <is>
@@ -5943,17 +5927,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AE25" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE25" s="20" t="n"/>
       <c r="AF25" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AG25" s="20" t="n"/>
+      <c r="AG25" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
@@ -5968,7 +5952,7 @@
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>Order approval detail + approve/reject</t>
+          <t>Order Approval Queue</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
@@ -5978,12 +5962,12 @@
       </c>
       <c r="E26" s="18" t="inlineStr">
         <is>
-          <t>SCR-061, SCR-062, SCR-063</t>
+          <t>SCR-060, SCR-197</t>
         </is>
       </c>
       <c r="F26" s="18" t="inlineStr">
         <is>
-          <t>Approve</t>
+          <t>View, Approve</t>
         </is>
       </c>
       <c r="G26" s="18" t="inlineStr">
@@ -5997,15 +5981,31 @@
       <c r="K26" s="20" t="n"/>
       <c r="L26" s="20" t="n"/>
       <c r="M26" s="20" t="n"/>
-      <c r="N26" s="20" t="n"/>
-      <c r="O26" s="20" t="n"/>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O26" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P26" s="20" t="n"/>
       <c r="Q26" s="20" t="n"/>
       <c r="R26" s="20" t="n"/>
       <c r="S26" s="20" t="n"/>
       <c r="T26" s="20" t="n"/>
-      <c r="U26" s="20" t="n"/>
-      <c r="V26" s="20" t="n"/>
+      <c r="U26" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W26" s="20" t="n"/>
       <c r="X26" s="20" t="n"/>
       <c r="Y26" s="20" t="n"/>
@@ -6022,7 +6022,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AE26" s="20" t="n"/>
+      <c r="AE26" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF26" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6043,25 +6047,29 @@
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>All Sales Orders / All SIM Swap Orders</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>Order approval detail + approve/reject</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="E27" s="18" t="inlineStr">
         <is>
-          <t>SCR-198</t>
+          <t>SCR-061, SCR-062, SCR-063</t>
         </is>
       </c>
       <c r="F27" s="18" t="inlineStr">
         <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr"/>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>Approve/reject is the only mutating action granted to this otherwise read-only role, per the role table's "approve or reject" wording</t>
+        </is>
+      </c>
       <c r="H27" s="20" t="n"/>
       <c r="I27" s="20" t="n"/>
       <c r="J27" s="20" t="n"/>
@@ -6069,26 +6077,14 @@
       <c r="L27" s="20" t="n"/>
       <c r="M27" s="20" t="n"/>
       <c r="N27" s="20" t="n"/>
-      <c r="O27" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O27" s="20" t="n"/>
       <c r="P27" s="20" t="n"/>
       <c r="Q27" s="20" t="n"/>
       <c r="R27" s="20" t="n"/>
       <c r="S27" s="20" t="n"/>
       <c r="T27" s="20" t="n"/>
-      <c r="U27" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="U27" s="20" t="n"/>
+      <c r="V27" s="20" t="n"/>
       <c r="W27" s="20" t="n"/>
       <c r="X27" s="20" t="n"/>
       <c r="Y27" s="20" t="n"/>
@@ -6106,7 +6102,11 @@
         </is>
       </c>
       <c r="AE27" s="20" t="n"/>
-      <c r="AF27" s="20" t="n"/>
+      <c r="AF27" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG27" s="20" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>Discount approval hierarchy</t>
+          <t>All Sales Orders / All SIM Swap Orders</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="E28" s="18" t="inlineStr">
         <is>
-          <t>SCR-011</t>
+          <t>SCR-198</t>
         </is>
       </c>
       <c r="F28" s="18" t="inlineStr">
         <is>
-          <t>View, Approve</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr"/>
@@ -6147,26 +6147,38 @@
       <c r="K28" s="20" t="n"/>
       <c r="L28" s="20" t="n"/>
       <c r="M28" s="20" t="n"/>
-      <c r="N28" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O28" s="20" t="n"/>
+      <c r="N28" s="20" t="n"/>
+      <c r="O28" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P28" s="20" t="n"/>
       <c r="Q28" s="20" t="n"/>
       <c r="R28" s="20" t="n"/>
       <c r="S28" s="20" t="n"/>
       <c r="T28" s="20" t="n"/>
-      <c r="U28" s="20" t="n"/>
-      <c r="V28" s="20" t="n"/>
+      <c r="U28" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W28" s="20" t="n"/>
       <c r="X28" s="20" t="n"/>
       <c r="Y28" s="20" t="n"/>
       <c r="Z28" s="20" t="n"/>
       <c r="AA28" s="20" t="n"/>
       <c r="AB28" s="20" t="n"/>
-      <c r="AC28" s="20" t="n"/>
+      <c r="AC28" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD28" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6184,27 +6196,27 @@
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
-          <t>Pre-to-Post Migration</t>
+          <t>Order Management</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>Pre-to-Post migration wizard</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>Built</t>
+          <t>Discount approval hierarchy</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="E29" s="18" t="inlineStr">
         <is>
-          <t>SCR-177, SCR-180</t>
+          <t>SCR-011</t>
         </is>
       </c>
       <c r="F29" s="18" t="inlineStr">
         <is>
-          <t>Create, Edit</t>
+          <t>View, Approve</t>
         </is>
       </c>
       <c r="G29" s="18" t="inlineStr"/>
@@ -6214,23 +6226,19 @@
       <c r="K29" s="20" t="n"/>
       <c r="L29" s="20" t="n"/>
       <c r="M29" s="20" t="n"/>
-      <c r="N29" s="20" t="n"/>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O29" s="20" t="n"/>
       <c r="P29" s="20" t="n"/>
       <c r="Q29" s="20" t="n"/>
       <c r="R29" s="20" t="n"/>
       <c r="S29" s="20" t="n"/>
-      <c r="T29" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T29" s="20" t="n"/>
       <c r="U29" s="20" t="n"/>
-      <c r="V29" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="V29" s="20" t="n"/>
       <c r="W29" s="20" t="n"/>
       <c r="X29" s="20" t="n"/>
       <c r="Y29" s="20" t="n"/>
@@ -6238,7 +6246,11 @@
       <c r="AA29" s="20" t="n"/>
       <c r="AB29" s="20" t="n"/>
       <c r="AC29" s="20" t="n"/>
-      <c r="AD29" s="20" t="n"/>
+      <c r="AD29" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE29" s="20" t="n"/>
       <c r="AF29" s="20" t="n"/>
       <c r="AG29" s="20" t="n"/>
@@ -6256,7 +6268,7 @@
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>Migration offer tab</t>
+          <t>Pre-to-Post migration wizard</t>
         </is>
       </c>
       <c r="D30" s="18" t="inlineStr">
@@ -6266,12 +6278,12 @@
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>SCR-179</t>
+          <t>SCR-177, SCR-180</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Create, Edit</t>
         </is>
       </c>
       <c r="G30" s="18" t="inlineStr"/>
@@ -6293,7 +6305,11 @@
         </is>
       </c>
       <c r="U30" s="20" t="n"/>
-      <c r="V30" s="20" t="n"/>
+      <c r="V30" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W30" s="20" t="n"/>
       <c r="X30" s="20" t="n"/>
       <c r="Y30" s="20" t="n"/>
@@ -6319,7 +6335,7 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>Bulk jobs / bulk processing dashboard</t>
+          <t>Migration offer tab</t>
         </is>
       </c>
       <c r="D31" s="18" t="inlineStr">
@@ -6329,12 +6345,12 @@
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>SCR-183</t>
+          <t>SCR-179</t>
         </is>
       </c>
       <c r="F31" s="18" t="inlineStr">
         <is>
-          <t>View, Edit</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="G31" s="18" t="inlineStr"/>
@@ -6350,33 +6366,21 @@
       <c r="Q31" s="20" t="n"/>
       <c r="R31" s="20" t="n"/>
       <c r="S31" s="20" t="n"/>
-      <c r="T31" s="20" t="n"/>
-      <c r="U31" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T31" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="20" t="n"/>
+      <c r="V31" s="20" t="n"/>
       <c r="W31" s="20" t="n"/>
       <c r="X31" s="20" t="n"/>
       <c r="Y31" s="20" t="n"/>
       <c r="Z31" s="20" t="n"/>
       <c r="AA31" s="20" t="n"/>
       <c r="AB31" s="20" t="n"/>
-      <c r="AC31" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD31" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC31" s="20" t="n"/>
+      <c r="AD31" s="20" t="n"/>
       <c r="AE31" s="20" t="n"/>
       <c r="AF31" s="20" t="n"/>
       <c r="AG31" s="20" t="n"/>
@@ -6394,7 +6398,7 @@
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>Connection details popup</t>
+          <t>Bulk jobs / bulk processing dashboard</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
@@ -6404,20 +6408,16 @@
       </c>
       <c r="E32" s="18" t="inlineStr">
         <is>
-          <t>SCR-075</t>
+          <t>SCR-183</t>
         </is>
       </c>
       <c r="F32" s="18" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>View, Edit</t>
         </is>
       </c>
       <c r="G32" s="18" t="inlineStr"/>
-      <c r="H32" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H32" s="20" t="n"/>
       <c r="I32" s="20" t="n"/>
       <c r="J32" s="20" t="n"/>
       <c r="K32" s="20" t="n"/>
@@ -6429,21 +6429,33 @@
       <c r="Q32" s="20" t="n"/>
       <c r="R32" s="20" t="n"/>
       <c r="S32" s="20" t="n"/>
-      <c r="T32" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="20" t="n"/>
-      <c r="V32" s="20" t="n"/>
+      <c r="T32" s="20" t="n"/>
+      <c r="U32" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W32" s="20" t="n"/>
       <c r="X32" s="20" t="n"/>
       <c r="Y32" s="20" t="n"/>
       <c r="Z32" s="20" t="n"/>
       <c r="AA32" s="20" t="n"/>
       <c r="AB32" s="20" t="n"/>
-      <c r="AC32" s="20" t="n"/>
-      <c r="AD32" s="20" t="n"/>
+      <c r="AC32" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AD32" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE32" s="20" t="n"/>
       <c r="AF32" s="20" t="n"/>
       <c r="AG32" s="20" t="n"/>
@@ -6456,12 +6468,12 @@
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
-          <t>SIM / Number Management</t>
+          <t>Pre-to-Post Migration</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>Number Management Portal</t>
+          <t>Connection details popup</t>
         </is>
       </c>
       <c r="D33" s="18" t="inlineStr">
@@ -6471,12 +6483,12 @@
       </c>
       <c r="E33" s="18" t="inlineStr">
         <is>
-          <t>SCR-024</t>
+          <t>SCR-075</t>
         </is>
       </c>
       <c r="F33" s="18" t="inlineStr">
         <is>
-          <t>View, Create, Edit</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G33" s="18" t="inlineStr"/>
@@ -6485,18 +6497,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I33" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I33" s="20" t="n"/>
       <c r="J33" s="20" t="n"/>
       <c r="K33" s="20" t="n"/>
-      <c r="L33" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L33" s="20" t="n"/>
       <c r="M33" s="20" t="n"/>
       <c r="N33" s="20" t="n"/>
       <c r="O33" s="20" t="n"/>
@@ -6504,15 +6508,15 @@
       <c r="Q33" s="20" t="n"/>
       <c r="R33" s="20" t="n"/>
       <c r="S33" s="20" t="n"/>
-      <c r="T33" s="20" t="n"/>
+      <c r="T33" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U33" s="20" t="n"/>
       <c r="V33" s="20" t="n"/>
       <c r="W33" s="20" t="n"/>
-      <c r="X33" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="X33" s="20" t="n"/>
       <c r="Y33" s="20" t="n"/>
       <c r="Z33" s="20" t="n"/>
       <c r="AA33" s="20" t="n"/>
@@ -6536,22 +6540,22 @@
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>TON (Transfer of Number) wizard</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>Number Management Portal</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>SCR-035</t>
+          <t>SCR-024</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>View, Create, Edit</t>
         </is>
       </c>
       <c r="G34" s="18" t="inlineStr"/>
@@ -6560,26 +6564,34 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I34" s="20" t="n"/>
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J34" s="20" t="n"/>
       <c r="K34" s="20" t="n"/>
-      <c r="L34" s="20" t="n"/>
+      <c r="L34" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M34" s="20" t="n"/>
       <c r="N34" s="20" t="n"/>
       <c r="O34" s="20" t="n"/>
       <c r="P34" s="20" t="n"/>
       <c r="Q34" s="20" t="n"/>
       <c r="R34" s="20" t="n"/>
-      <c r="S34" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S34" s="20" t="n"/>
       <c r="T34" s="20" t="n"/>
       <c r="U34" s="20" t="n"/>
       <c r="V34" s="20" t="n"/>
       <c r="W34" s="20" t="n"/>
-      <c r="X34" s="20" t="n"/>
+      <c r="X34" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Y34" s="20" t="n"/>
       <c r="Z34" s="20" t="n"/>
       <c r="AA34" s="20" t="n"/>
@@ -6603,22 +6615,22 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>SIM swap queue</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>Built</t>
+          <t>TON (Transfer of Number) wizard</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
-          <t>SCR-196</t>
+          <t>SCR-035</t>
         </is>
       </c>
       <c r="F35" s="18" t="inlineStr">
         <is>
-          <t>Create, Edit</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="G35" s="18" t="inlineStr"/>
@@ -6635,11 +6647,7 @@
       <c r="N35" s="20" t="n"/>
       <c r="O35" s="20" t="n"/>
       <c r="P35" s="20" t="n"/>
-      <c r="Q35" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q35" s="20" t="n"/>
       <c r="R35" s="20" t="n"/>
       <c r="S35" s="19" t="inlineStr">
         <is>
@@ -6647,22 +6655,10 @@
         </is>
       </c>
       <c r="T35" s="20" t="n"/>
-      <c r="U35" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="U35" s="20" t="n"/>
+      <c r="V35" s="20" t="n"/>
       <c r="W35" s="20" t="n"/>
-      <c r="X35" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="X35" s="20" t="n"/>
       <c r="Y35" s="20" t="n"/>
       <c r="Z35" s="20" t="n"/>
       <c r="AA35" s="20" t="n"/>
@@ -6686,7 +6682,7 @@
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>Global search screen</t>
+          <t>SIM swap queue</t>
         </is>
       </c>
       <c r="D36" s="18" t="inlineStr">
@@ -6696,12 +6692,12 @@
       </c>
       <c r="E36" s="18" t="inlineStr">
         <is>
-          <t>SCR-195</t>
+          <t>SCR-196</t>
         </is>
       </c>
       <c r="F36" s="18" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Create, Edit</t>
         </is>
       </c>
       <c r="G36" s="18" t="inlineStr"/>
@@ -6710,58 +6706,26 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I36" s="20" t="n"/>
+      <c r="J36" s="20" t="n"/>
       <c r="K36" s="20" t="n"/>
-      <c r="L36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="L36" s="20" t="n"/>
+      <c r="M36" s="20" t="n"/>
+      <c r="N36" s="20" t="n"/>
+      <c r="O36" s="20" t="n"/>
       <c r="P36" s="20" t="n"/>
       <c r="Q36" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R36" s="20" t="n"/>
       <c r="S36" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="T36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T36" s="20" t="n"/>
       <c r="U36" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6772,57 +6736,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="W36" s="20" t="n"/>
       <c r="X36" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Y36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Z36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y36" s="20" t="n"/>
+      <c r="Z36" s="20" t="n"/>
+      <c r="AA36" s="20" t="n"/>
       <c r="AB36" s="20" t="n"/>
-      <c r="AC36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG36" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC36" s="20" t="n"/>
+      <c r="AD36" s="20" t="n"/>
+      <c r="AE36" s="20" t="n"/>
+      <c r="AF36" s="20" t="n"/>
+      <c r="AG36" s="20" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="17" t="inlineStr">
@@ -6832,12 +6760,12 @@
       </c>
       <c r="B37" s="18" t="inlineStr">
         <is>
-          <t>Trouble Ticketing / Complaints</t>
+          <t>SIM / Number Management</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>Tickets dashboard</t>
+          <t>Global search screen</t>
         </is>
       </c>
       <c r="D37" s="18" t="inlineStr">
@@ -6847,12 +6775,12 @@
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
-          <t>SCR-211</t>
+          <t>SCR-195</t>
         </is>
       </c>
       <c r="F37" s="18" t="inlineStr">
         <is>
-          <t>View, Create, Edit, Full</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G37" s="18" t="inlineStr"/>
@@ -6866,21 +6794,33 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J37" s="20" t="n"/>
+      <c r="J37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K37" s="20" t="n"/>
       <c r="L37" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="M37" s="20" t="n"/>
-      <c r="N37" s="20" t="n"/>
-      <c r="O37" s="20" t="n"/>
-      <c r="P37" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P37" s="20" t="n"/>
       <c r="Q37" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6901,16 +6841,36 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="20" t="n"/>
-      <c r="V37" s="20" t="n"/>
-      <c r="W37" s="20" t="n"/>
+      <c r="U37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="X37" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Y37" s="20" t="n"/>
-      <c r="Z37" s="20" t="n"/>
+      <c r="Y37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AA37" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6927,7 +6887,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AE37" s="20" t="n"/>
+      <c r="AE37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF37" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6952,7 +6916,7 @@
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Ticket detail &amp; public notes</t>
+          <t>Tickets dashboard</t>
         </is>
       </c>
       <c r="D38" s="18" t="inlineStr">
@@ -6962,7 +6926,7 @@
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
-          <t>SCR-029, SCR-210</t>
+          <t>SCR-211</t>
         </is>
       </c>
       <c r="F38" s="18" t="inlineStr">
@@ -6970,11 +6934,7 @@
           <t>View, Create, Edit, Full</t>
         </is>
       </c>
-      <c r="G38" s="18" t="inlineStr">
-        <is>
-          <t>Cannot set Resolution Code - resolution is owned by the Complaints Agent role</t>
-        </is>
-      </c>
+      <c r="G38" s="18" t="inlineStr"/>
       <c r="H38" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7035,11 +6995,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AB38" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AB38" s="20" t="n"/>
       <c r="AC38" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7075,34 +7031,54 @@
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Ticket field templates (per issue type)</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>Ticket detail &amp; public notes</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
-          <t>SCR-213</t>
+          <t>SCR-029, SCR-210</t>
         </is>
       </c>
       <c r="F39" s="18" t="inlineStr">
         <is>
-          <t>View, Edit, Full</t>
-        </is>
-      </c>
-      <c r="G39" s="18" t="inlineStr"/>
-      <c r="H39" s="20" t="n"/>
-      <c r="I39" s="20" t="n"/>
+          <t>View, Create, Edit, Full</t>
+        </is>
+      </c>
+      <c r="G39" s="18" t="inlineStr">
+        <is>
+          <t>Cannot set Resolution Code - resolution is owned by the Complaints Agent role</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I39" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J39" s="20" t="n"/>
       <c r="K39" s="20" t="n"/>
-      <c r="L39" s="20" t="n"/>
+      <c r="L39" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M39" s="20" t="n"/>
       <c r="N39" s="20" t="n"/>
       <c r="O39" s="20" t="n"/>
-      <c r="P39" s="20" t="n"/>
+      <c r="P39" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q39" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7113,16 +7089,36 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="20" t="n"/>
-      <c r="T39" s="20" t="n"/>
+      <c r="S39" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T39" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U39" s="20" t="n"/>
       <c r="V39" s="20" t="n"/>
       <c r="W39" s="20" t="n"/>
-      <c r="X39" s="20" t="n"/>
+      <c r="X39" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Y39" s="20" t="n"/>
       <c r="Z39" s="20" t="n"/>
-      <c r="AA39" s="20" t="n"/>
-      <c r="AB39" s="20" t="n"/>
+      <c r="AA39" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AB39" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AC39" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7133,12 +7129,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AE39" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF39" s="20" t="n"/>
+      <c r="AE39" s="20" t="n"/>
+      <c r="AF39" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG39" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7153,55 +7149,35 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Identity / Customer Management</t>
+          <t>Trouble Ticketing / Complaints</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Passport-to-QID update wizard</t>
-        </is>
-      </c>
-      <c r="D40" s="18" t="inlineStr">
-        <is>
-          <t>Built</t>
+          <t>Ticket field templates (per issue type)</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="E40" s="18" t="inlineStr">
         <is>
-          <t>SCR-151</t>
+          <t>SCR-213</t>
         </is>
       </c>
       <c r="F40" s="18" t="inlineStr">
         <is>
-          <t>Create, Edit, Full</t>
+          <t>View, Edit, Full</t>
         </is>
       </c>
       <c r="G40" s="18" t="inlineStr"/>
-      <c r="H40" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I40" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J40" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K40" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="L40" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H40" s="20" t="n"/>
+      <c r="I40" s="20" t="n"/>
+      <c r="J40" s="20" t="n"/>
+      <c r="K40" s="20" t="n"/>
+      <c r="L40" s="20" t="n"/>
       <c r="M40" s="20" t="n"/>
       <c r="N40" s="20" t="n"/>
       <c r="O40" s="20" t="n"/>
@@ -7211,34 +7187,42 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="R40" s="20" t="n"/>
-      <c r="S40" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R40" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="20" t="n"/>
       <c r="T40" s="20" t="n"/>
       <c r="U40" s="20" t="n"/>
-      <c r="V40" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W40" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="V40" s="20" t="n"/>
+      <c r="W40" s="20" t="n"/>
       <c r="X40" s="20" t="n"/>
       <c r="Y40" s="20" t="n"/>
       <c r="Z40" s="20" t="n"/>
       <c r="AA40" s="20" t="n"/>
       <c r="AB40" s="20" t="n"/>
-      <c r="AC40" s="20" t="n"/>
-      <c r="AD40" s="20" t="n"/>
-      <c r="AE40" s="20" t="n"/>
+      <c r="AC40" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AD40" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE40" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF40" s="20" t="n"/>
-      <c r="AG40" s="20" t="n"/>
+      <c r="AG40" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
@@ -7253,37 +7237,65 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Person administration</t>
-        </is>
-      </c>
-      <c r="D41" s="21" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>Passport-to-QID update wizard</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
-          <t>SCR-054</t>
+          <t>SCR-151</t>
         </is>
       </c>
       <c r="F41" s="18" t="inlineStr">
         <is>
-          <t>View, Edit, Full</t>
+          <t>Create, Edit, Full</t>
         </is>
       </c>
       <c r="G41" s="18" t="inlineStr"/>
-      <c r="H41" s="20" t="n"/>
-      <c r="I41" s="20" t="n"/>
-      <c r="J41" s="20" t="n"/>
-      <c r="K41" s="20" t="n"/>
-      <c r="L41" s="20" t="n"/>
+      <c r="H41" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I41" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K41" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L41" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="M41" s="20" t="n"/>
       <c r="N41" s="20" t="n"/>
       <c r="O41" s="20" t="n"/>
       <c r="P41" s="20" t="n"/>
-      <c r="Q41" s="20" t="n"/>
+      <c r="Q41" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R41" s="20" t="n"/>
-      <c r="S41" s="20" t="n"/>
+      <c r="S41" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T41" s="20" t="n"/>
       <c r="U41" s="20" t="n"/>
       <c r="V41" s="19" t="inlineStr">
@@ -7303,11 +7315,7 @@
       <c r="AB41" s="20" t="n"/>
       <c r="AC41" s="20" t="n"/>
       <c r="AD41" s="20" t="n"/>
-      <c r="AE41" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE41" s="20" t="n"/>
       <c r="AF41" s="20" t="n"/>
       <c r="AG41" s="20" t="n"/>
     </row>
@@ -7324,7 +7332,7 @@
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Agent 360 / asset summary</t>
+          <t>Person administration</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
@@ -7334,12 +7342,12 @@
       </c>
       <c r="E42" s="18" t="inlineStr">
         <is>
-          <t>SCR-022</t>
+          <t>SCR-054</t>
         </is>
       </c>
       <c r="F42" s="18" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>View, Edit, Full</t>
         </is>
       </c>
       <c r="G42" s="18" t="inlineStr"/>
@@ -7357,7 +7365,11 @@
       <c r="S42" s="20" t="n"/>
       <c r="T42" s="20" t="n"/>
       <c r="U42" s="20" t="n"/>
-      <c r="V42" s="20" t="n"/>
+      <c r="V42" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W42" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7370,7 +7382,11 @@
       <c r="AB42" s="20" t="n"/>
       <c r="AC42" s="20" t="n"/>
       <c r="AD42" s="20" t="n"/>
-      <c r="AE42" s="20" t="n"/>
+      <c r="AE42" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF42" s="20" t="n"/>
       <c r="AG42" s="20" t="n"/>
     </row>
@@ -7382,49 +7398,37 @@
       </c>
       <c r="B43" s="18" t="inlineStr">
         <is>
-          <t>Enterprise / IoT / B2B</t>
+          <t>Identity / Customer Management</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>Enterprise account creation</t>
-        </is>
-      </c>
-      <c r="D43" s="18" t="inlineStr">
-        <is>
-          <t>Built</t>
+          <t>Agent 360 / asset summary</t>
+        </is>
+      </c>
+      <c r="D43" s="21" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
-          <t>SCR-007</t>
+          <t>SCR-022</t>
         </is>
       </c>
       <c r="F43" s="18" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>View</t>
         </is>
       </c>
       <c r="G43" s="18" t="inlineStr"/>
       <c r="H43" s="20" t="n"/>
       <c r="I43" s="20" t="n"/>
-      <c r="J43" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J43" s="20" t="n"/>
       <c r="K43" s="20" t="n"/>
       <c r="L43" s="20" t="n"/>
-      <c r="M43" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="N43" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="M43" s="20" t="n"/>
+      <c r="N43" s="20" t="n"/>
       <c r="O43" s="20" t="n"/>
       <c r="P43" s="20" t="n"/>
       <c r="Q43" s="20" t="n"/>
@@ -7433,7 +7437,11 @@
       <c r="T43" s="20" t="n"/>
       <c r="U43" s="20" t="n"/>
       <c r="V43" s="20" t="n"/>
-      <c r="W43" s="20" t="n"/>
+      <c r="W43" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="X43" s="20" t="n"/>
       <c r="Y43" s="20" t="n"/>
       <c r="Z43" s="20" t="n"/>
@@ -7458,7 +7466,7 @@
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>Bulk adjustment portal</t>
+          <t>Enterprise account creation</t>
         </is>
       </c>
       <c r="D44" s="18" t="inlineStr">
@@ -7468,18 +7476,22 @@
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>SCR-001</t>
+          <t>SCR-007</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="G44" s="18" t="inlineStr"/>
       <c r="H44" s="20" t="n"/>
       <c r="I44" s="20" t="n"/>
-      <c r="J44" s="20" t="n"/>
+      <c r="J44" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K44" s="20" t="n"/>
       <c r="L44" s="20" t="n"/>
       <c r="M44" s="19" t="inlineStr">
@@ -7499,18 +7511,10 @@
       <c r="S44" s="20" t="n"/>
       <c r="T44" s="20" t="n"/>
       <c r="U44" s="20" t="n"/>
-      <c r="V44" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="V44" s="20" t="n"/>
       <c r="W44" s="20" t="n"/>
       <c r="X44" s="20" t="n"/>
-      <c r="Y44" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Y44" s="20" t="n"/>
       <c r="Z44" s="20" t="n"/>
       <c r="AA44" s="20" t="n"/>
       <c r="AB44" s="20" t="n"/>
@@ -7533,32 +7537,28 @@
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Billing profile grid (account level)</t>
-        </is>
-      </c>
-      <c r="D45" s="21" t="inlineStr">
-        <is>
-          <t>Planned</t>
+          <t>Bulk adjustment portal</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr">
         <is>
-          <t>SCR-186</t>
+          <t>SCR-001</t>
         </is>
       </c>
       <c r="F45" s="18" t="inlineStr">
         <is>
-          <t>View, Edit</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="G45" s="18" t="inlineStr"/>
       <c r="H45" s="20" t="n"/>
       <c r="I45" s="20" t="n"/>
-      <c r="J45" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J45" s="20" t="n"/>
       <c r="K45" s="20" t="n"/>
       <c r="L45" s="20" t="n"/>
       <c r="M45" s="19" t="inlineStr">
@@ -7574,15 +7574,15 @@
       <c r="O45" s="20" t="n"/>
       <c r="P45" s="20" t="n"/>
       <c r="Q45" s="20" t="n"/>
-      <c r="R45" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R45" s="20" t="n"/>
       <c r="S45" s="20" t="n"/>
       <c r="T45" s="20" t="n"/>
       <c r="U45" s="20" t="n"/>
-      <c r="V45" s="20" t="n"/>
+      <c r="V45" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W45" s="20" t="n"/>
       <c r="X45" s="20" t="n"/>
       <c r="Y45" s="19" t="inlineStr">
@@ -7590,11 +7590,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Z45" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Z45" s="20" t="n"/>
       <c r="AA45" s="20" t="n"/>
       <c r="AB45" s="20" t="n"/>
       <c r="AC45" s="20" t="n"/>
@@ -7611,12 +7607,12 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>Billing &amp; Adjustments</t>
+          <t>Enterprise / IoT / B2B</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>Statement of Account view</t>
+          <t>Billing profile grid (account level)</t>
         </is>
       </c>
       <c r="D46" s="21" t="inlineStr">
@@ -7626,7 +7622,7 @@
       </c>
       <c r="E46" s="18" t="inlineStr">
         <is>
-          <t>SCR-003</t>
+          <t>SCR-186</t>
         </is>
       </c>
       <c r="F46" s="18" t="inlineStr">
@@ -7637,7 +7633,11 @@
       <c r="G46" s="18" t="inlineStr"/>
       <c r="H46" s="20" t="n"/>
       <c r="I46" s="20" t="n"/>
-      <c r="J46" s="20" t="n"/>
+      <c r="J46" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K46" s="20" t="n"/>
       <c r="L46" s="20" t="n"/>
       <c r="M46" s="19" t="inlineStr">
@@ -7651,26 +7651,14 @@
         </is>
       </c>
       <c r="O46" s="20" t="n"/>
-      <c r="P46" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P46" s="20" t="n"/>
+      <c r="Q46" s="20" t="n"/>
       <c r="R46" s="19" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S46" s="20" t="n"/>
       <c r="T46" s="20" t="n"/>
       <c r="U46" s="20" t="n"/>
       <c r="V46" s="20" t="n"/>
@@ -7688,23 +7676,11 @@
       </c>
       <c r="AA46" s="20" t="n"/>
       <c r="AB46" s="20" t="n"/>
-      <c r="AC46" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD46" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC46" s="20" t="n"/>
+      <c r="AD46" s="20" t="n"/>
       <c r="AE46" s="20" t="n"/>
       <c r="AF46" s="20" t="n"/>
-      <c r="AG46" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG46" s="20" t="n"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="17" t="inlineStr">
@@ -7719,7 +7695,7 @@
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>Bill simulation</t>
+          <t>Statement of Account view</t>
         </is>
       </c>
       <c r="D47" s="21" t="inlineStr">
@@ -7729,7 +7705,7 @@
       </c>
       <c r="E47" s="18" t="inlineStr">
         <is>
-          <t>SCR-005</t>
+          <t>SCR-003</t>
         </is>
       </c>
       <c r="F47" s="18" t="inlineStr">
@@ -7743,13 +7719,37 @@
       <c r="J47" s="20" t="n"/>
       <c r="K47" s="20" t="n"/>
       <c r="L47" s="20" t="n"/>
-      <c r="M47" s="20" t="n"/>
-      <c r="N47" s="20" t="n"/>
+      <c r="M47" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="N47" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O47" s="20" t="n"/>
-      <c r="P47" s="20" t="n"/>
-      <c r="Q47" s="20" t="n"/>
-      <c r="R47" s="20" t="n"/>
-      <c r="S47" s="20" t="n"/>
+      <c r="P47" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T47" s="20" t="n"/>
       <c r="U47" s="20" t="n"/>
       <c r="V47" s="20" t="n"/>
@@ -7767,11 +7767,23 @@
       </c>
       <c r="AA47" s="20" t="n"/>
       <c r="AB47" s="20" t="n"/>
-      <c r="AC47" s="20" t="n"/>
-      <c r="AD47" s="20" t="n"/>
+      <c r="AC47" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AD47" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE47" s="20" t="n"/>
       <c r="AF47" s="20" t="n"/>
-      <c r="AG47" s="20" t="n"/>
+      <c r="AG47" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
@@ -7781,12 +7793,12 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>CAF, Attachments &amp; Forms</t>
+          <t>Billing &amp; Adjustments</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>Product promotions administration</t>
+          <t>Bill simulation</t>
         </is>
       </c>
       <c r="D48" s="21" t="inlineStr">
@@ -7796,12 +7808,12 @@
       </c>
       <c r="E48" s="18" t="inlineStr">
         <is>
-          <t>SCR-117, SCR-118</t>
+          <t>SCR-005</t>
         </is>
       </c>
       <c r="F48" s="18" t="inlineStr">
         <is>
-          <t>Edit, Full</t>
+          <t>View, Edit</t>
         </is>
       </c>
       <c r="G48" s="18" t="inlineStr"/>
@@ -7812,11 +7824,7 @@
       <c r="L48" s="20" t="n"/>
       <c r="M48" s="20" t="n"/>
       <c r="N48" s="20" t="n"/>
-      <c r="O48" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O48" s="20" t="n"/>
       <c r="P48" s="20" t="n"/>
       <c r="Q48" s="20" t="n"/>
       <c r="R48" s="20" t="n"/>
@@ -7826,21 +7834,21 @@
       <c r="V48" s="20" t="n"/>
       <c r="W48" s="20" t="n"/>
       <c r="X48" s="20" t="n"/>
-      <c r="Y48" s="20" t="n"/>
-      <c r="Z48" s="20" t="n"/>
+      <c r="Y48" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z48" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AA48" s="20" t="n"/>
       <c r="AB48" s="20" t="n"/>
       <c r="AC48" s="20" t="n"/>
-      <c r="AD48" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE48" s="19" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD48" s="20" t="n"/>
+      <c r="AE48" s="20" t="n"/>
       <c r="AF48" s="20" t="n"/>
       <c r="AG48" s="20" t="n"/>
     </row>
@@ -7852,12 +7860,12 @@
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>Platform Governance &amp; Architecture</t>
+          <t>CAF, Attachments &amp; Forms</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>Integration / service bus monitor</t>
+          <t>Product promotions administration</t>
         </is>
       </c>
       <c r="D49" s="21" t="inlineStr">
@@ -7867,12 +7875,12 @@
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
-          <t>SCR-016, SCR-065</t>
+          <t>SCR-117, SCR-118</t>
         </is>
       </c>
       <c r="F49" s="18" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Edit, Full</t>
         </is>
       </c>
       <c r="G49" s="18" t="inlineStr"/>
@@ -7883,7 +7891,11 @@
       <c r="L49" s="20" t="n"/>
       <c r="M49" s="20" t="n"/>
       <c r="N49" s="20" t="n"/>
-      <c r="O49" s="20" t="n"/>
+      <c r="O49" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P49" s="20" t="n"/>
       <c r="Q49" s="20" t="n"/>
       <c r="R49" s="20" t="n"/>
@@ -7898,7 +7910,11 @@
       <c r="AA49" s="20" t="n"/>
       <c r="AB49" s="20" t="n"/>
       <c r="AC49" s="20" t="n"/>
-      <c r="AD49" s="20" t="n"/>
+      <c r="AD49" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE49" s="19" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7907,8 +7923,71 @@
       <c r="AF49" s="20" t="n"/>
       <c r="AG49" s="20" t="n"/>
     </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>FEAT-048</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>Platform Governance &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>Integration / service bus monitor</t>
+        </is>
+      </c>
+      <c r="D50" s="21" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>SCR-016, SCR-065</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="G50" s="18" t="inlineStr"/>
+      <c r="H50" s="20" t="n"/>
+      <c r="I50" s="20" t="n"/>
+      <c r="J50" s="20" t="n"/>
+      <c r="K50" s="20" t="n"/>
+      <c r="L50" s="20" t="n"/>
+      <c r="M50" s="20" t="n"/>
+      <c r="N50" s="20" t="n"/>
+      <c r="O50" s="20" t="n"/>
+      <c r="P50" s="20" t="n"/>
+      <c r="Q50" s="20" t="n"/>
+      <c r="R50" s="20" t="n"/>
+      <c r="S50" s="20" t="n"/>
+      <c r="T50" s="20" t="n"/>
+      <c r="U50" s="20" t="n"/>
+      <c r="V50" s="20" t="n"/>
+      <c r="W50" s="20" t="n"/>
+      <c r="X50" s="20" t="n"/>
+      <c r="Y50" s="20" t="n"/>
+      <c r="Z50" s="20" t="n"/>
+      <c r="AA50" s="20" t="n"/>
+      <c r="AB50" s="20" t="n"/>
+      <c r="AC50" s="20" t="n"/>
+      <c r="AD50" s="20" t="n"/>
+      <c r="AE50" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF50" s="20" t="n"/>
+      <c r="AG50" s="20" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:G49"/>
+  <autoFilter ref="A2:G50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9236,7 +9315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9641,17 +9720,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>workspace.task-detail</t>
+          <t>workspace.qnomy-ticket-history</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Task detail</t>
+          <t>My Ticket History (Qnomy)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Tasks</t>
+          <t>Front Desk</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -9670,11 +9749,11 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Edit, Full</t>
+          <t>View</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
@@ -9687,17 +9766,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>workspace.agent-profile</t>
+          <t>workspace.task-detail</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Agent profile</t>
+          <t>Task detail</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Agent Profile</t>
+          <t>Tasks</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -9716,11 +9795,11 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>View, Edit</t>
+          <t>Edit, Full</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr"/>
@@ -9733,17 +9812,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>workspace.admin-role-access-viewer</t>
+          <t>workspace.agent-profile</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Administration - roles &amp; access viewer</t>
+          <t>Agent profile</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Agent Profile</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -9762,11 +9841,11 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>View, Full</t>
+          <t>View, Edit</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr"/>
@@ -9779,22 +9858,22 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>fixedline.new-fixed-line-wizard</t>
+          <t>workspace.admin-role-access-viewer</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>New Fixed Line guided wizard</t>
+          <t>Administration - roles &amp; access viewer</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Fixed Line / Fibre</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>module</t>
+          <t>workspace</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -9804,7 +9883,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>SCR-043, SCR-045, SCR-046, SCR-048, SCR-050, SCR-058</t>
+          <t>—  (routed directly)</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
@@ -9812,7 +9891,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>View, Full</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr"/>
@@ -9825,12 +9904,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>fixedline.wfm-activity-details</t>
+          <t>fixedline.new-fixed-line-wizard</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>WFM Activity Details - Admin/Technician view</t>
+          <t>New Fixed Line guided wizard</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -9843,22 +9922,22 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>SCR-110</t>
+          <t>SCR-043, SCR-045, SCR-046, SCR-048, SCR-050, SCR-058</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>View, Edit, Full</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr"/>
@@ -9871,17 +9950,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>fwa.new-fwa-wizard</t>
+          <t>fixedline.wfm-activity-details</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>New FWA / 5G Home guided wizard</t>
+          <t>WFM Activity Details - Admin/Technician view</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>FWA / 5G Home</t>
+          <t>Fixed Line / Fibre</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -9889,14 +9968,14 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Built</t>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>SCR-077, SCR-078, SCR-079, SCR-080, SCR-082, SCR-084, SCR-085</t>
+          <t>SCR-110</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
@@ -9904,7 +9983,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>View, Edit, Full</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr"/>
@@ -9917,12 +9996,12 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>fwa.serial-number-check</t>
+          <t>fwa.new-fwa-wizard</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Serial number check (Dual Play)</t>
+          <t>New FWA / 5G Home guided wizard</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -9942,15 +10021,15 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>SCR-093</t>
+          <t>SCR-077, SCR-078, SCR-079, SCR-080, SCR-082, SCR-084, SCR-085</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>View, Create</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr"/>
@@ -9963,12 +10042,12 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>fwa.appointment-booking</t>
+          <t>fwa.serial-number-check</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Appointment booking &amp; calendar</t>
+          <t>Serial number check (Dual Play)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -9981,22 +10060,22 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>SCR-028, SCR-049, SCR-083, SCR-086, SCR-109, SCR-115</t>
+          <t>SCR-093</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>View, Create, Edit, Full</t>
+          <t>View, Create</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr"/>
@@ -10009,17 +10088,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>postpaid.new-postpaid-wizard</t>
+          <t>fwa.appointment-booking</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>New Postpaid Connection wizard</t>
+          <t>Appointment booking &amp; calendar</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Mobile Postpaid</t>
+          <t>FWA / 5G Home</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -10027,14 +10106,14 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Built</t>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>SCR-037, SCR-154, SCR-155, SCR-156, SCR-157, SCR-158, SCR-159, SCR-160, SCR-161, SCR-162</t>
+          <t>SCR-028, SCR-049, SCR-083, SCR-086, SCR-109, SCR-115</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
@@ -10042,14 +10121,10 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Create</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Smart Limit / Bill Limit editable only down to the Agent Minimum Value</t>
-        </is>
-      </c>
+          <t>View, Create, Edit, Full</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -10059,17 +10134,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>prepaid.new-prepaid-tablet-wizard</t>
+          <t>postpaid.new-postpaid-wizard</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>New Prepaid (Tablet) wizard</t>
+          <t>New Postpaid Connection wizard</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Mobile Prepaid</t>
+          <t>Mobile Postpaid</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -10084,18 +10159,22 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>SCR-190, SCR-191, SCR-192</t>
+          <t>SCR-037, SCR-154, SCR-155, SCR-156, SCR-157, SCR-158, SCR-159, SCR-160, SCR-161, SCR-162</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Create</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Smart Limit / Bill Limit editable only down to the Agent Minimum Value</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -10105,17 +10184,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>mnp.process-choice</t>
+          <t>prepaid.new-prepaid-tablet-wizard</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>MNP process choice gate</t>
+          <t>New Prepaid (Tablet) wizard</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>MNP / FNP Porting</t>
+          <t>Mobile Prepaid</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10130,15 +10209,15 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>SCR-120</t>
+          <t>SCR-190, SCR-191, SCR-192</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>View, Create, Full</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr"/>
@@ -10151,12 +10230,12 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>mnp.port-in-wizard</t>
+          <t>mnp.process-choice</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>MNP Port-In guided wizard</t>
+          <t>MNP process choice gate</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -10176,15 +10255,15 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>SCR-121, SCR-122, SCR-123, SCR-124, SCR-125, SCR-126, SCR-127, SCR-129, SCR-132, SCR-133, SCR-134</t>
+          <t>SCR-120</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Create, Full</t>
+          <t>View, Create, Full</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr"/>
@@ -10197,17 +10276,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>leads.list-views</t>
+          <t>mnp.port-in-wizard</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Lead list views (My / Created / Team / All / Contact)</t>
+          <t>MNP Port-In guided wizard</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Lead Management</t>
+          <t>MNP / FNP Porting</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -10222,15 +10301,15 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>SCR-142, SCR-143, SCR-144, SCR-147, SCR-150</t>
+          <t>SCR-121, SCR-122, SCR-123, SCR-124, SCR-125, SCR-126, SCR-127, SCR-129, SCR-132, SCR-133, SCR-134</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>View, Edit</t>
+          <t>Create, Full</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr"/>
@@ -10243,12 +10322,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>leads.detail-actions</t>
+          <t>leads.list-views</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Lead detail &amp; lead actions</t>
+          <t>Lead list views (My / Created / Team / All / Contact)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -10268,15 +10347,15 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>SCR-141, SCR-145, SCR-146, SCR-148, SCR-149</t>
+          <t>SCR-142, SCR-143, SCR-144, SCR-147, SCR-150</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>View, Edit</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr"/>
@@ -10289,17 +10368,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>orders.my-sales-orders</t>
+          <t>leads.detail-actions</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>My Sales Orders queue</t>
+          <t>Lead detail &amp; lead actions</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Order Management</t>
+          <t>Lead Management</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -10314,15 +10393,15 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>SCR-059</t>
+          <t>SCR-141, SCR-145, SCR-146, SCR-148, SCR-149</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>View, Create, Edit</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr"/>
@@ -10335,12 +10414,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>orders.approval-queue</t>
+          <t>orders.my-sales-orders</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Order Approval Queue</t>
+          <t>My Sales Orders queue</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -10360,22 +10439,18 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>SCR-060, SCR-197</t>
+          <t>SCR-059</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>View, Approve</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>Approve/reject is the only mutating action granted to this otherwise read-only role, per the role table's "approve or reject" wording</t>
-        </is>
-      </c>
+          <t>View, Create, Edit</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -10385,12 +10460,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>orders.approval-detail</t>
+          <t>orders.approval-queue</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Order approval detail + approve/reject</t>
+          <t>Order Approval Queue</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -10410,15 +10485,15 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>SCR-061, SCR-062, SCR-063</t>
+          <t>SCR-060, SCR-197</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Approve</t>
+          <t>View, Approve</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -10435,12 +10510,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>orders.all-sales-orders</t>
+          <t>orders.approval-detail</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>All Sales Orders / All SIM Swap Orders</t>
+          <t>Order approval detail + approve/reject</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -10453,25 +10528,29 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>SCR-198</t>
+          <t>SCR-061, SCR-062, SCR-063</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr"/>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Approve/reject is the only mutating action granted to this otherwise read-only role, per the role table's "approve or reject" wording</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -10481,12 +10560,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>orders.discount-approval-hierarchy</t>
+          <t>orders.all-sales-orders</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Discount approval hierarchy</t>
+          <t>All Sales Orders / All SIM Swap Orders</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -10506,15 +10585,15 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>SCR-011</t>
+          <t>SCR-198</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>View, Approve</t>
+          <t>View</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr"/>
@@ -10527,17 +10606,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>migration.pre-to-post-wizard</t>
+          <t>orders.discount-approval-hierarchy</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Pre-to-Post migration wizard</t>
+          <t>Discount approval hierarchy</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Pre-to-Post Migration</t>
+          <t>Order Management</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -10545,14 +10624,14 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Built</t>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>SCR-177, SCR-180</t>
+          <t>SCR-011</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
@@ -10560,7 +10639,7 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Create, Edit</t>
+          <t>View, Approve</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr"/>
@@ -10573,12 +10652,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>migration.offer-tab</t>
+          <t>migration.pre-to-post-wizard</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Migration offer tab</t>
+          <t>Pre-to-Post migration wizard</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -10598,15 +10677,15 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>SCR-179</t>
+          <t>SCR-177, SCR-180</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Create, Edit</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr"/>
@@ -10619,12 +10698,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>migration.bulk-jobs</t>
+          <t>migration.offer-tab</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Bulk jobs / bulk processing dashboard</t>
+          <t>Migration offer tab</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -10644,15 +10723,15 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>SCR-183</t>
+          <t>SCR-179</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>View, Edit</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr"/>
@@ -10665,12 +10744,12 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>migration.connection-details</t>
+          <t>migration.bulk-jobs</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Connection details popup</t>
+          <t>Bulk jobs / bulk processing dashboard</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -10690,15 +10769,15 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>SCR-075</t>
+          <t>SCR-183</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>View, Edit</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
@@ -10711,17 +10790,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>numbers.management-portal</t>
+          <t>migration.connection-details</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Number Management Portal</t>
+          <t>Connection details popup</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>SIM / Number Management</t>
+          <t>Pre-to-Post Migration</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -10736,15 +10815,15 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>SCR-024</t>
+          <t>SCR-075</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>View, Create, Edit</t>
+          <t>View</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr"/>
@@ -10757,12 +10836,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>numbers.ton-wizard</t>
+          <t>numbers.management-portal</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>TON (Transfer of Number) wizard</t>
+          <t>Number Management Portal</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -10775,22 +10854,22 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>SCR-035</t>
+          <t>SCR-024</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>View, Create, Edit</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
@@ -10803,12 +10882,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>numbers.sim-swap-queue</t>
+          <t>numbers.ton-wizard</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>SIM swap queue</t>
+          <t>TON (Transfer of Number) wizard</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -10821,22 +10900,22 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Built</t>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>SCR-196</t>
+          <t>SCR-035</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Create, Edit</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr"/>
@@ -10849,12 +10928,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>search.global-search-screen</t>
+          <t>numbers.sim-swap-queue</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Global search screen</t>
+          <t>SIM swap queue</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -10874,15 +10953,15 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>SCR-195</t>
+          <t>SCR-196</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Create, Edit</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr"/>
@@ -10895,17 +10974,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>tickets.dashboard</t>
+          <t>search.global-search-screen</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Tickets dashboard</t>
+          <t>Global search screen</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Trouble Ticketing / Complaints</t>
+          <t>SIM / Number Management</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -10920,15 +10999,15 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>SCR-211</t>
+          <t>SCR-195</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>View, Create, Edit, Full</t>
+          <t>View</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr"/>
@@ -10941,12 +11020,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>tickets.detail-view</t>
+          <t>tickets.dashboard</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Ticket detail &amp; public notes</t>
+          <t>Tickets dashboard</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -10966,22 +11045,18 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>SCR-029, SCR-210</t>
+          <t>SCR-211</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>View, Create, Edit, Full</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>Cannot set Resolution Code - resolution is owned by the Complaints Agent role</t>
-        </is>
-      </c>
+      <c r="J37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -10991,12 +11066,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>tickets.field-templates</t>
+          <t>tickets.detail-view</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Ticket field templates (per issue type)</t>
+          <t>Ticket detail &amp; public notes</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -11009,25 +11084,29 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>SCR-213</t>
+          <t>SCR-029, SCR-210</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>View, Edit, Full</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr"/>
+          <t>View, Create, Edit, Full</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Cannot set Resolution Code - resolution is owned by the Complaints Agent role</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -11037,17 +11116,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>identity.passport-to-qid</t>
+          <t>tickets.field-templates</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Passport-to-QID update wizard</t>
+          <t>Ticket field templates (per issue type)</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Identity / Customer Management</t>
+          <t>Trouble Ticketing / Complaints</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -11055,22 +11134,22 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Built</t>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>SCR-151</t>
+          <t>SCR-213</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Create, Edit, Full</t>
+          <t>View, Edit, Full</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr"/>
@@ -11083,12 +11162,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>identity.person-administration</t>
+          <t>identity.passport-to-qid</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Person administration</t>
+          <t>Passport-to-QID update wizard</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -11101,22 +11180,22 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>SCR-054</t>
+          <t>SCR-151</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>View, Edit, Full</t>
+          <t>Create, Edit, Full</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr"/>
@@ -11129,12 +11208,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>identity.agent-360-asset-summary</t>
+          <t>identity.person-administration</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Agent 360 / asset summary</t>
+          <t>Person administration</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -11154,15 +11233,15 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>SCR-022</t>
+          <t>SCR-054</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>View, Edit, Full</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr"/>
@@ -11175,17 +11254,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>enterprise.account-creation</t>
+          <t>identity.agent-360-asset-summary</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Enterprise account creation</t>
+          <t>Agent 360 / asset summary</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Enterprise / IoT / B2B</t>
+          <t>Identity / Customer Management</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -11193,22 +11272,22 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Built</t>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>SCR-007</t>
+          <t>SCR-022</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>View</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr"/>
@@ -11221,12 +11300,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>enterprise.bulk-adjustment-portal</t>
+          <t>enterprise.account-creation</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Bulk adjustment portal</t>
+          <t>Enterprise account creation</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -11246,15 +11325,15 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>SCR-001</t>
+          <t>SCR-007</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Edit</t>
+          <t>Create</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr"/>
@@ -11267,12 +11346,12 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>enterprise.billing-profile-grid</t>
+          <t>enterprise.bulk-adjustment-portal</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Billing profile grid (account level)</t>
+          <t>Bulk adjustment portal</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -11285,22 +11364,22 @@
           <t>module</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>Planned</t>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Built</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>SCR-186</t>
+          <t>SCR-001</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>View, Edit</t>
+          <t>Edit</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr"/>
@@ -11313,17 +11392,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>billing.statement-of-account</t>
+          <t>enterprise.billing-profile-grid</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Statement of Account view</t>
+          <t>Billing profile grid (account level)</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Billing &amp; Adjustments</t>
+          <t>Enterprise / IoT / B2B</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -11338,11 +11417,11 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>SCR-003</t>
+          <t>SCR-186</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
@@ -11359,12 +11438,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>billing.bill-simulation</t>
+          <t>billing.statement-of-account</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Bill simulation</t>
+          <t>Statement of Account view</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -11384,11 +11463,11 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>SCR-005</t>
+          <t>SCR-003</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
@@ -11405,17 +11484,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>admin.product-promotions</t>
+          <t>billing.bill-simulation</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Product promotions administration</t>
+          <t>Bill simulation</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>CAF, Attachments &amp; Forms</t>
+          <t>Billing &amp; Adjustments</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -11430,15 +11509,15 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>SCR-117, SCR-118</t>
+          <t>SCR-005</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Edit, Full</t>
+          <t>View, Edit</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr"/>
@@ -11451,46 +11530,92 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
+          <t>admin.product-promotions</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Product promotions administration</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>CAF, Attachments &amp; Forms</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>module</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>SCR-117, SCR-118</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Edit, Full</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>FEAT-048</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
           <t>platform.integration-monitor</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Integration / service bus monitor</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Platform Governance &amp; Architecture</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>SCR-016, SCR-065</t>
         </is>
       </c>
-      <c r="H48" s="2" t="n">
+      <c r="H49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="J48" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J48"/>
+  <autoFilter ref="A1:J49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15570,7 +15695,7 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>47 catalogued (34 built, 13 planned).</t>
+          <t>48 catalogued (35 built, 13 planned).</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15786,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>c957121</t>
+          <t>2b26a68</t>
         </is>
       </c>
     </row>

--- a/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
+++ b/vfq-dxp-app/reference/VFQ_DXP_Persona_Feature_Applicability_Matrix_Reference.xlsx
@@ -15786,7 +15786,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2b26a68</t>
+          <t>6da4fa1</t>
         </is>
       </c>
     </row>
